--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -9,8 +9,11 @@
   <sheets>
     <sheet name="NHÂN SỰ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CHƯƠNG TRÌNH HỌC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="QUY ĐỊNH" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HƯỚNG DẪN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="QUY ĐỊNH CHUNG" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="QUY ĐỊNH NGÀY" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="QUY ĐỊNH TIẾT" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="QUY ĐỊNH MÔN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="HƯỚNG DẪN" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1918,12 +1921,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1946,425 +1949,94 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ngày học</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 2, Thứ 3, Thứ 4, Thứ 5, Thứ 6</t>
-        </is>
+          <t>Số tiết buổi sáng</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Các ngày học, liền nhau từ Thứ 2 (có thể thêm Thứ 7). Ngày nào cũng học buổi sáng.</t>
+          <t>Buổi sáng là tiết 1 đến tiết này.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ngày học buổi chiều</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 2, Thứ 3, Thứ 4, Thứ 5</t>
-        </is>
+          <t>Số tiết buổi chiều</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Các ngày có buổi chiều; để trống là không học buổi chiều.</t>
+          <t>Buổi chiều là các tiết tiếp theo, vd sáng 4 tiết, chiều 3 tiết thì chiều là tiết 5, 6, 7.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Số tiết buổi sáng</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Số tiết tối đa một nhóm môn mỗi buổi</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Buổi sáng là tiết 1 đến tiết này.</t>
+          <t>Luật cứng; môn có từ 2 tiết trong một buổi thì các tiết đó phải liền nhau.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Số tiết buổi chiều</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Ghép cặp khi nhóm môn có từ (tiết/tuần)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Buổi chiều là các tiết tiếp theo, vd sáng 4 tiết, chiều 3 tiết thì chiều là tiết 5, 6, 7.</t>
+          <t>Luật cứng: nhóm môn có từ ngần ấy tiết/tuần và tổng số tiết chẵn thì xếp thành các cặp 2 tiết liền, cùng người dạy (trừ nhóm ghi Có ở cột Không ghép cặp, sheet QUY ĐỊNH MÔN).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Môn HĐTN</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Hoạt động trải nghiệm</t>
+          <t>Chủ Nhiệm được dạy bù</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Môn chào cờ, sinh hoạt lớp: có các tiết cố định dưới đây.</t>
+          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Tiết HĐTN cố định</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 2 tiết 1, Thứ 6 tiết 4</t>
+          <t>Bộ Môn được dạy bù</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: mọi lớp học môn HĐTN đúng các ô này, vd Thứ 2 tiết 1, Thứ 6 tiết 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Ngày xếp tiết HĐTN còn lại</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 3, Thứ 4, Thứ 5</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Tiết luôn do GVCN dạy</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy; để trống là không có.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Môn GVCN nhận trọn</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt, Toán, Hoạt động trải nghiệm, Khoa học, Lịch sử - Địa lý, Đạo đức</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Thứ tự cắt khi GVCN vượt định mức</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt, Toán, Khoa học, Lịch sử - Địa lý</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Các môn trên vượt định mức thì cắt bớt theo thứ tự này, mỗi môn GVCN giữ ít nhất 1 tiết.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Thứ tự nhận thêm khi GVCN thiếu định mức</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt tăng cường, Toán tăng cường, Tự nhiên xã hội, Kỹ năng sống, Công nghệ</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>GVCN nhận thêm các môn này theo thứ tự cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Môn chỉ GVCN dạy</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Hoạt động trải nghiệm</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Môn GV bộ môn không dạy</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Hoạt động trải nghiệm, Tin học, Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>GV bộ môn dạy được mọi môn trừ các môn này; môn chưa có GV chuyên biệt thì chương trình tuyển thêm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Quản lý dạy</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống khối 4</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Môn và khối quản lý được dạy, vd Kỹ năng sống khối 4; chỉ vài lớp: Kỹ năng sống khối 4 lớp 4/1, 4/2. Nhiều mục cách nhau bằng dấu chấm phẩy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Chức vụ được dạy bù</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Chủ Nhiệm, Bộ Môn</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ ghi Chủ Nhiệm, Bộ Môn. GVCN chỉ bù ở lớp mình và bù trước; bộ môn bù khi GVCN đã bù hết mức.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Môn chuyên biệt GVCN được bù</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật, Âm nhạc</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Môn của GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Môn tăng cường đi với môn chính</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt tăng cường = Tiếng Việt; Toán tăng cường = Toán</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi mục: môn tăng cường = môn chính, cách nhau bằng dấu chấm phẩy. Hai môn tính chung một nhóm môn; luật cứng: tiết tăng cường đứng sau mọi tiết chính trong ngày và ngày đó phải có tiết chính.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Số tiết tối đa một nhóm môn mỗi buổi</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Luật cứng; môn có từ 2 tiết trong một buổi thì các tiết đó phải liền nhau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Số tiết tối đa mỗi ngày của môn</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Toán = 1</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Luật cứng, vd Toán = 1; chỉ áp dụng khi số tiết/tuần của môn không quá số ngày học.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Ghép cặp 2 tiết liền khi nhóm môn có từ</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Luật cứng: nhóm môn có từ ngần ấy tiết/tuần và tổng số tiết chẵn thì xếp thành các cặp 2 tiết liền, cùng người dạy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Nhóm môn không ghép cặp</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Hoạt động trải nghiệm, Toán</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Các nhóm môn (ghi môn chính) không áp dụng luật ghép cặp ở trên.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Môn nặng</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học, Tin học, Tiếng Anh, Tiếng Việt, Tiếng Việt tăng cường, Toán, Toán tăng cường</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Mục tiêu mềm: hạn chế xếp các môn này vào các tiết ở dòng dưới.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Tiết hạn chế môn nặng</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Mục tiêu mềm: mỗi tiết môn nặng ở các tiết này bị trừ điểm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Môn ưu tiên buổi sáng</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt, Toán</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Mục tiêu mềm: mỗi tiết các môn này ở buổi chiều bị trừ điểm, và các môn này được rải đều hơn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Tên môn viết tắt trong TKB</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Hoạt động trải nghiệm = HĐTN; Tự nhiên xã hội = TNXH; Tiếng Việt tăng cường = TV tăng cường</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi mục: tên môn = chữ ghi trong ô TKB, cách nhau bằng dấu chấm phẩy; môn khác ghi đúng tên.</t>
+          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2051,1316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Học buổi sáng</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Học buổi chiều</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tiết HĐTN cố định</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Xếp tiết HĐTN còn lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 2</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 3</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 5</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tiết</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Luôn do GVCN dạy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Hạn chế môn nặng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Môn học</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tên trong TKB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Môn HĐTN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>GVCN nhận trọn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>GVCN cắt bớt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GVCN nhận thêm</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Chỉ GVCN dạy</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Bộ Môn không dạy</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Quản lý dạy khối</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>GVCN bù môn chuyên biệt</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Nhóm môn</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Môn tăng cường</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Tối đa tiết mỗi ngày</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Không ghép cặp</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Môn nặng</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ưu tiên buổi sáng</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Hoạt động trải nghiệm</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>HĐTN</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Tin học</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt tăng cường</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>TV tăng cường</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Toán</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Tự nhiên xã hội</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>TNXH</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2514,7 +3495,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Buổi không xếp tiết: buổi cố định (vd Chiều T5, Sáng T6) hoặc số buổi bất kỳ (vd 2 buổi chiều), cách nhau bằng dấu phẩy. GVCN không nghỉ buổi sáng được (tiết luôn do GVCN dạy ở sheet QUY ĐỊNH).</t>
+          <t>Buổi không xếp tiết: buổi cố định (vd Chiều T5, Sáng T6) hoặc số buổi bất kỳ (vd 2 buổi chiều), cách nhau bằng dấu phẩy. GVCN không nghỉ buổi sáng được (tiết Luôn do GVCN dạy ở sheet QUY ĐỊNH TIẾT).</t>
         </is>
       </c>
     </row>
@@ -2526,53 +3507,329 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng: cột Môn học ghi tên môn, cột Khối k ghi số tiết/tuần của môn ở khối k (0 hoặc để trống: khối đó không học). Dùng lại đúng tên môn này ở cột Chức Vụ và sheet QUY ĐỊNH.</t>
+          <t>Mỗi môn một dòng: cột Môn học ghi tên môn, cột Khối k ghi số tiết/tuần của môn ở khối k (0 hoặc để trống: khối đó không học). Dùng lại đúng tên môn này ở cột Chức Vụ và sheet QUY ĐỊNH MÔN.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH</t>
+          <t>Các sheet QUY ĐỊNH</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Các luật nghiệp vụ, mỗi dòng một quy định: chỉ sửa cột Giá trị, cột Ghi chú giải thích. Xóa một dòng thì chương trình dùng giá trị mặc định của quy định đó; không có sheet này thì mọi quy định dùng giá trị mặc định.</t>
+          <t>Các luật nghiệp vụ, mỗi quy định một cột (sheet QUY ĐỊNH CHUNG: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của sheet chung, hoặc cả sheet) thì quy định đó dùng giá trị mặc định của chương trình.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: tên môn</t>
+          <t>QUY ĐỊNH CHUNG</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Ghi như trong sheet CHƯƠNG TRÌNH HỌC (không phân biệt hoa thường); nhiều môn cách nhau bằng dấu phẩy; để trống là không có môn nào.</t>
+          <t>Mỗi dòng một quy định, ghi ở cột Giá trị; cột Ghi chú giải thích.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: ngày, tiết</t>
+          <t>QUY ĐỊNH NGÀY</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Ngày ghi Thứ 2 … Thứ 7. Tiết ghi số: buổi sáng từ tiết 1, buổi chiều nối tiếp buổi sáng (sáng 4 tiết thì chiều từ tiết 5). Ô cố định ghi dạng Thứ 2 tiết 1.</t>
+          <t>Mỗi ngày Thứ 2 … Thứ 7 một dòng.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>QUY ĐỊNH TIẾT</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi tiết một dòng; buổi chiều đánh số nối tiếp buổi sáng (sáng 4 tiết thì chiều từ tiết 5). Thêm tiết thì thêm dòng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi môn một dòng, tên như trong sheet CHƯƠNG TRÌNH HỌC (không phân biệt hoa thường). Môn không có dòng thì mọi cột là Không.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH NGÀY: Học buổi sáng</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Các ngày học, liền nhau từ Thứ 2 (có thể thêm Thứ 7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH NGÀY: Học buổi chiều</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Ngày có buổi chiều (phải là ngày học buổi sáng).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH NGÀY: Tiết HĐTN cố định</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH NGÀY: Xếp tiết HĐTN còn lại</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH TIẾT: Luôn do GVCN dạy</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH TIẾT: Hạn chế môn nặng</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Tên trong TKB</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Môn HĐTN</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở sheet QUY ĐỊNH NGÀY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: GVCN nhận trọn</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Số thứ tự 1, 2...: GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: GVCN cắt bớt</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Số thứ tự cắt khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: GVCN nhận thêm</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Số thứ tự nhận thêm cho đủ định mức GVCN (không nhận môn của GV chuyên biệt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Chỉ GVCN dạy</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Bộ Môn không dạy</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="25" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Quản lý dạy khối</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Khối mà Quản Lý được dạy môn này, vd Kỹ năng sống: 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="25" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: GVCN bù môn chuyên biệt</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="25" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Nhóm môn</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="25" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Môn tăng cường</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="25" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Tối đa tiết mỗi ngày</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Luật cứng, vd Toán: 1; chỉ áp dụng khi số tiết/tuần của môn không quá số ngày học.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="25" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Không ghép cặp</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="25" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Môn nặng</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (QUY ĐỊNH TIẾT).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="25" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH MÔN: Ưu tiên buổi sáng</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="25" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -9,11 +9,8 @@
   <sheets>
     <sheet name="NHÂN SỰ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CHƯƠNG TRÌNH HỌC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="QUY ĐỊNH CHUNG" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="QUY ĐỊNH NGÀY" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="QUY ĐỊNH TIẾT" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="QUY ĐỊNH MÔN" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="HƯỚNG DẪN" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="QUY ĐỊNH" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="HƯỚNG DẪN" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1787,7 +1784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1796,6 +1793,21 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1829,86 +1841,1298 @@
           <t>Khối 5</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tên trong TKB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Môn HĐTN</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>GVCN nhận trọn</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>GVCN cắt bớt</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>GVCN nhận thêm</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Chỉ GVCN dạy</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Bộ Môn không dạy</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Quản lý dạy khối</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>GVCN bù môn chuyên biệt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Nhóm môn</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Môn tăng cường</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tối đa tiết mỗi ngày</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Không ghép cặp</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Môn nặng</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Ưu tiên buổi sáng</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="3" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt</t>
+        </is>
+      </c>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="3" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Toán</t>
+        </is>
+      </c>
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="3" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Hoạt động trải nghiệm</t>
+        </is>
+      </c>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>HĐTN</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="3" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học</t>
+        </is>
+      </c>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="3" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý</t>
+        </is>
+      </c>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="3" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức</t>
+        </is>
+      </c>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="3" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt tăng cường</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TV tăng cường</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="3" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường</t>
+        </is>
+      </c>
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="3" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Tự nhiên xã hội</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>TNXH</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="3" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống</t>
+        </is>
+      </c>
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Tin học</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n"/>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n"/>
+      <c r="T18" s="3" t="n"/>
+      <c r="U18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="3" t="n"/>
+      <c r="U19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="3" t="n"/>
+      <c r="T20" s="3" t="n"/>
+      <c r="U20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n"/>
+      <c r="U21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n"/>
+      <c r="Q22" s="3" t="n"/>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="3" t="n"/>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n"/>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="n"/>
+      <c r="U23" s="3" t="n"/>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="3" t="n"/>
+      <c r="Q24" s="3" t="n"/>
+      <c r="R24" s="3" t="n"/>
+      <c r="S24" s="3" t="n"/>
+      <c r="T24" s="3" t="n"/>
+      <c r="U24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n"/>
+      <c r="Q25" s="3" t="n"/>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="n"/>
+      <c r="T25" s="3" t="n"/>
+      <c r="U25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="3" t="n"/>
+      <c r="Q26" s="3" t="n"/>
+      <c r="R26" s="3" t="n"/>
+      <c r="S26" s="3" t="n"/>
+      <c r="T26" s="3" t="n"/>
+      <c r="U26" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1921,12 +3145,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1940,11 +3166,6 @@
           <t>Giá trị</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1955,11 +3176,6 @@
       <c r="B2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Buổi sáng là tiết 1 đến tiết này.</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -1970,11 +3186,6 @@
       <c r="B3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Buổi chiều là các tiết tiếp theo, vd sáng 4 tiết, chiều 3 tiết thì chiều là tiết 5, 6, 7.</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1985,11 +3196,6 @@
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Luật cứng; môn có từ 2 tiết trong một buổi thì các tiết đó phải liền nhau.</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -2000,11 +3206,6 @@
       <c r="B5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Luật cứng: nhóm môn có từ ngần ấy tiết/tuần và tổng số tiết chẵn thì xếp thành các cặp 2 tiết liền, cùng người dạy (trừ nhóm ghi Có ở cột Không ghép cặp, sheet QUY ĐỊNH MÔN).</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -2017,11 +3218,6 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -2034,9 +3230,295 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Học buổi sáng</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Học buổi chiều</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Tiết HĐTN cố định</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Xếp tiết HĐTN còn lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 2</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 3</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 5</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 7</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Tiết</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Luôn do GVCN dạy</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Hạn chế môn nặng</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
         </is>
       </c>
     </row>
@@ -2051,1316 +3533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Ngày</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Học buổi sáng</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Học buổi chiều</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Tiết HĐTN cố định</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Xếp tiết HĐTN còn lại</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 2</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 3</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 4</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 5</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 6</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 7</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tiết</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Luôn do GVCN dạy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Hạn chế môn nặng</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="21" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Môn học</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Tên trong TKB</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Môn HĐTN</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>GVCN nhận trọn</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>GVCN cắt bớt</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>GVCN nhận thêm</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Chỉ GVCN dạy</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Bộ Môn không dạy</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Quản lý dạy khối</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>GVCN bù môn chuyên biệt</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Nhóm môn</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Môn tăng cường</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Tối đa tiết mỗi ngày</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Không ghép cặp</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Môn nặng</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Ưu tiên buổi sáng</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Hoạt động trải nghiệm</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>HĐTN</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Tin học</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt tăng cường</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>TV tăng cường</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Toán</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Tự nhiên xã hội</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>TNXH</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3495,7 +3668,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Buổi không xếp tiết: buổi cố định (vd Chiều T5, Sáng T6) hoặc số buổi bất kỳ (vd 2 buổi chiều), cách nhau bằng dấu phẩy. GVCN không nghỉ buổi sáng được (tiết Luôn do GVCN dạy ở sheet QUY ĐỊNH TIẾT).</t>
+          <t>Buổi không xếp tiết: buổi cố định (vd Chiều T5, Sáng T6) hoặc số buổi bất kỳ (vd 2 buổi chiều), cách nhau bằng dấu phẩy. GVCN không nghỉ buổi sáng được (tiết Luôn do GVCN dạy ở sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
@@ -3507,329 +3680,365 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng: cột Môn học ghi tên môn, cột Khối k ghi số tiết/tuần của môn ở khối k (0 hoặc để trống: khối đó không học). Dùng lại đúng tên môn này ở cột Chức Vụ và sheet QUY ĐỊNH MÔN.</t>
+          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở cột Chức Vụ của GV chuyên biệt), cột Khối k ghi số tiết/tuần của môn ở khối k (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Các sheet QUY ĐỊNH</t>
+          <t>Quy ước các ô quy định</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Các luật nghiệp vụ, mỗi quy định một cột (sheet QUY ĐỊNH CHUNG: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của sheet chung, hoặc cả sheet) thì quy định đó dùng giá trị mặc định của chương trình.</t>
+          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH CHUNG</t>
+          <t>QUY ĐỊNH</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Mỗi dòng một quy định, ghi ở cột Giá trị; cột Ghi chú giải thích.</t>
+          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (Thứ 2 … Thứ 7); Tiết (buổi chiều đánh số nối tiếp buổi sáng, sáng 4 tiết thì chiều từ tiết 5; thêm tiết thì thêm dòng).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH NGÀY</t>
+          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Mỗi ngày Thứ 2 … Thứ 7 một dòng.</t>
+          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH TIẾT</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Mỗi tiết một dòng; buổi chiều đánh số nối tiếp buổi sáng (sáng 4 tiết thì chiều từ tiết 5). Thêm tiết thì thêm dòng.</t>
+          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng, tên như trong sheet CHƯƠNG TRÌNH HỌC (không phân biệt hoa thường). Môn không có dòng thì mọi cột là Không.</t>
+          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH NGÀY: Học buổi sáng</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Các ngày học, liền nhau từ Thứ 2 (có thể thêm Thứ 7).</t>
+          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH NGÀY: Học buổi chiều</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Ngày có buổi chiều (phải là ngày học buổi sáng).</t>
+          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH NGÀY: Tiết HĐTN cố định</t>
+          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
+          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH NGÀY: Xếp tiết HĐTN còn lại</t>
+          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH TIẾT: Luôn do GVCN dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+          <t>Khối mà Quản Lý được dạy môn này, vd Kỹ năng sống: 4.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH TIẾT: Hạn chế môn nặng</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Tên trong TKB</t>
+          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
+          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Môn HĐTN</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở sheet QUY ĐỊNH NGÀY.</t>
+          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: GVCN nhận trọn</t>
+          <t>CHƯƠNG TRÌNH HỌC: Tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
+          <t>Luật cứng, vd Toán: 1; chỉ áp dụng khi số tiết/tuần của môn không quá số ngày học.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: GVCN cắt bớt</t>
+          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự cắt khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
+          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: GVCN nhận thêm</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự nhận thêm cho đủ định mức GVCN (không nhận môn của GV chuyên biệt).</t>
+          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Chỉ GVCN dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
+          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Bộ Môn không dạy</t>
+          <t>QUY ĐỊNH: Số tiết buổi sáng</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm.</t>
+          <t>Buổi sáng là tiết 1 đến tiết này.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Quản lý dạy khối</t>
+          <t>QUY ĐỊNH: Số tiết buổi chiều</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Khối mà Quản Lý được dạy môn này, vd Kỹ năng sống: 4.</t>
+          <t>Buổi chiều là các tiết tiếp theo, vd sáng 4 tiết, chiều 3 tiết thì chiều là tiết 5, 6, 7.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: GVCN bù môn chuyên biệt</t>
+          <t>QUY ĐỊNH: Số tiết tối đa một nhóm môn mỗi buổi</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
+          <t>Luật cứng; môn có từ 2 tiết trong một buổi thì các tiết đó phải liền nhau.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Nhóm môn</t>
+          <t>QUY ĐỊNH: Ghép cặp khi nhóm môn có từ (tiết/tuần)</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
+          <t>Luật cứng: nhóm môn có từ ngần ấy tiết/tuần và tổng số tiết chẵn thì xếp thành các cặp 2 tiết liền, cùng người dạy (trừ môn ghi Có ở cột Không ghép cặp).</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Môn tăng cường</t>
+          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
+          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Tối đa tiết mỗi ngày</t>
+          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng, vd Toán: 1; chỉ áp dụng khi số tiết/tuần của môn không quá số ngày học.</t>
+          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Không ghép cặp</t>
+          <t>QUY ĐỊNH: Học buổi sáng</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền.</t>
+          <t>Các ngày học, liền nhau từ Thứ 2 (có thể thêm Thứ 7).</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Môn nặng</t>
+          <t>QUY ĐỊNH: Học buổi chiều</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (QUY ĐỊNH TIẾT).</t>
+          <t>Ngày có buổi chiều (phải là ngày học buổi sáng).</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH MÔN: Ưu tiên buổi sáng</t>
+          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
+          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="25" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -10,7 +10,8 @@
     <sheet name="NHÂN SỰ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CHƯƠNG TRÌNH HỌC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="QUY ĐỊNH" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HƯỚNG DẪN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LUẬT RIÊNG" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="HƯỚNG DẪN" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3533,7 +3534,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kiểu luật</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Môn</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Môn thứ hai</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Khối</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tiết</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Buổi</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Giáo viên</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Số</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Bắt buộc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Mức</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4035,10 +4250,94 @@
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>LUẬT RIÊNG</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Không bắt buộc. Mỗi dòng một luật riêng của trường: chọn Kiểu luật rồi ghi các cột kiểu đó dùng (cột không dùng để trống). Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên, ô trống là Không); Mức: 1, 2, 3 (chỉ cho luật ưu tiên, trống là 2, 3 là ưu tiên nhất). Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc tên môn của GV chuyên biệt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Không xếp vào</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Môn (của các khối ở cột Khối; trống: mọi khối) không học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không học tiết 1; Tin học không học Thứ 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="25" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Chỉ xếp vào</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Môn chỉ học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ học buổi chiều.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Học 2 tiết liền</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (cả môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Học trước</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Giáo viên tối đa tiết mỗi ngày</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="25" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Số lớp học cùng lúc tối đa</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Môn có tối đa Số lớp học cùng một tiết (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="25" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="NHÂN SỰ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CHƯƠNG TRÌNH HỌC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="QUY ĐỊNH" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LUẬT RIÊNG" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="HƯỚNG DẪN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CHỨC VỤ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="QUY ĐỊNH" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LUẬT RIÊNG" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="HƯỚNG DẪN" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3146,6 +3147,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Chức vụ</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Môn được dạy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3528,7 +3599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3742,13 +3813,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3799,7 +3870,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Chủ Nhiệm, Bộ Môn, Quản Lý hoặc tên một môn trong sheet CHƯƠNG TRÌNH HỌC (GV chuyên biệt). Không ghi số thứ tự: chương trình tự đánh số theo thứ tự dòng.</t>
+          <t>Chủ Nhiệm, Bộ Môn, Quản Lý, một chức vụ của sheet CHỨC VỤ hoặc tên một môn trong sheet CHƯƠNG TRÌNH HỌC (GV chuyên biệt). Không ghi số thứ tự: chương trình tự đánh số theo thứ tự dòng.</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3966,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở cột Chức Vụ của GV chuyên biệt), cột Khối k ghi số tiết/tuần của môn ở khối k (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn.</t>
+          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối k ghi số tiết/tuần của môn ở khối k (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn.</t>
         </is>
       </c>
     </row>
@@ -4250,94 +4321,106 @@
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG</t>
+          <t>CHỨC VỤ</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một luật riêng của trường: chọn Kiểu luật rồi ghi các cột kiểu đó dùng (cột không dùng để trống). Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên, ô trống là Không); Mức: 1, 2, 3 (chỉ cho luật ưu tiên, trống là 2, 3 là ưu tiên nhất). Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc tên môn của GV chuyên biệt).</t>
+          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Không xếp vào</t>
+          <t>LUẬT RIÊNG</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; trống: mọi khối) không học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không học tiết 1; Tin học không học Thứ 2.</t>
+          <t>Không bắt buộc. Mỗi dòng một luật riêng của trường: chọn Kiểu luật rồi ghi các cột kiểu đó dùng (cột không dùng để trống). Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên, ô trống là Không); Mức: 1, 2, 3 (chỉ cho luật ưu tiên, trống là 2, 3 là ưu tiên nhất). Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt, vd Tiếng Anh).</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Chỉ xếp vào</t>
+          <t>LUẬT RIÊNG: Không xếp vào</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ học buổi chiều.</t>
+          <t>Môn (của các khối ở cột Khối; trống: mọi khối) không học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không học tiết 1; Tin học không học Thứ 2.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Học 2 tiết liền</t>
+          <t>LUẬT RIÊNG: Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (cả môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Môn chỉ học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ học buổi chiều.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Học trước</t>
+          <t>LUẬT RIÊNG: Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (cả môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT RIÊNG: Học trước</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT RIÊNG: Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một tiết (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>LUẬT RIÊNG: Số lớp học cùng lúc tối đa</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Môn có tối đa Số lớp học cùng một tiết (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="25" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3629,50 +3629,90 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Với mỗi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Môn</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Gồm môn tăng cường</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Nhãn</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Khối</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lớp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Tiết</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Buổi</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Giáo viên</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Phép đo</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>So sánh</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Số</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Đếm theo</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Môn thứ hai</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Khối</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Ngày</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Tiết</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Buổi</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Giáo viên</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Số</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Áp dụng khi</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Bắt buộc</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Mức</t>
         </is>
@@ -3690,6 +3730,14 @@
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" s="3" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="n"/>
@@ -3703,6 +3751,14 @@
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="n"/>
@@ -3716,6 +3772,14 @@
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="n"/>
@@ -3729,6 +3793,14 @@
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="n"/>
@@ -3742,6 +3814,14 @@
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="n"/>
@@ -3755,6 +3835,14 @@
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="n"/>
@@ -3768,6 +3856,14 @@
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="n"/>
@@ -3781,6 +3877,14 @@
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="n"/>
@@ -3794,6 +3898,14 @@
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="n"/>
@@ -3807,6 +3919,14 @@
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3819,7 +3939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4338,7 +4458,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một luật riêng của trường: chọn Kiểu luật rồi ghi các cột kiểu đó dùng (cột không dùng để trống). Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên, ô trống là Không); Mức: 1, 2, 3 (chỉ cho luật ưu tiên, trống là 2, 3 là ưu tiên nhất). Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt, vd Tiếng Anh).</t>
+          <t>Không bắt buộc. Mỗi dòng một luật riêng của trường: chọn Kiểu luật (một mẫu, hoặc Tự ghép) rồi ghi các cột kiểu đó dùng (cột không dùng để trống). Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên, ô trống là Không); Mức: 1, 2, 3 (chỉ cho luật ưu tiên, trống là 2, 3 là ưu tiên nhất). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt, vd Tiếng Anh). Nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của ngày, tiết (vd Luôn do GVCN dạy). Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -4417,10 +4537,202 @@
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>LUẬT RIÊNG: Cố định vào</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi tiết ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định Thứ 3 tiết 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="25" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Giáo viên tối đa lớp mỗi ngày</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="25" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Học ít nhất số ngày</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="25" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Chỉ giáo viên dạy</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên có chức vụ ở cột Giáo viên dạy, vd Tin học khối 3 chỉ Tin Học dạy; tiết 1 Thứ 2 chỉ Chủ Nhiệm dạy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="25" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Ghép câu luật: Với mỗi [phạm vi], các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] thì [Phép đo] [So sánh] [Số], khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="25" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, cột Với mỗi</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="25" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, Phép đo Số tiết</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày tối đa 1 tiết Toán; mỗi giờ học tối đa 1 lớp Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="25" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, Phép đo Số khác nhau</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Số giá trị khác nhau ở cột Đếm theo, vd mỗi GV mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="25" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, Phép đo Vị trí</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Các tiết chỉ nằm trong / không nằm trong các ngày, tiết, buổi (và nhãn ngày, tiết) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="25" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, Phép đo Liền nhau</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Các tiết trong mỗi buổi (của mỗi lớp hoặc GV) đứng liền nhau, không có tiết khác xen giữa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="25" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, Phép đo Theo cặp 2 tiết</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi buổi 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: không có tiết lẻ đứng một mình).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="25" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, Phép đo Thứ tự</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Trong mỗi buổi (hoặc ngày, nếu phạm vi có Ngày) các tiết ở cột Môn đứng trước các tiết Môn thứ hai. Ghi cột Môn thứ hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="25" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, Phép đo Đi kèm</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Buổi (hoặc ngày) có tiết ở cột Môn thì cũng có tiết Môn thứ hai. Ghi cột Môn thứ hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="25" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, Phép đo Người dạy</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Các tiết do GV có chức vụ ở cột Giáo viên dạy; hoặc mọi tiết trong mỗi phạm vi do cùng một người. So sánh: Do, Cùng một người.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="25" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, Phép đo Khoảng cách</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Số tiết trống giữa các tiết trong buổi tối đa ngần ấy; hoặc mỗi tiết cách cuối buổi tối đa ngần ấy tiết. So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="25" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT RIÊNG: Tự ghép, cột Áp dụng khi</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ áp dụng cho khối mà số tiết/tuần của các môn ở cột Môn thỏa điều kiện, vd '&gt;= 6, chẵn' hoặc '&lt;= số ngày'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="25" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -11,7 +11,7 @@
     <sheet name="CHƯƠNG TRÌNH HỌC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="CHỨC VỤ" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="QUY ĐỊNH" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="LUẬT RIÊNG" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="LUẬT" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="HƯỚNG DẪN" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -1786,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1806,10 +1806,9 @@
     <col width="27" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1900,20 +1899,15 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Tối đa tiết mỗi ngày</t>
+          <t>Không ghép cặp</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Không ghép cặp</t>
+          <t>Môn nặng</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Môn nặng</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Ưu tiên buổi sáng</t>
         </is>
@@ -1969,18 +1963,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R2" s="3" t="n"/>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
@@ -2036,8 +2029,10 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R3" s="3" t="n">
-        <v>1</v>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
@@ -2045,11 +2040,6 @@
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
@@ -2105,18 +2095,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R4" s="3" t="n"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2170,18 +2159,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R5" s="3" t="n"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2235,18 +2223,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R6" s="3" t="n"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2298,18 +2285,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R7" s="3" t="n"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2369,18 +2355,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="R8" s="3" t="n"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2436,18 +2421,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="R9" s="3" t="n"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2505,18 +2489,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R10" s="3" t="n"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2572,18 +2555,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R11" s="3" t="n"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2637,18 +2619,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R12" s="3" t="n"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2700,18 +2681,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R13" s="3" t="n"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2763,18 +2743,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R14" s="3" t="n"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2826,18 +2805,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R15" s="3" t="n"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2889,18 +2867,17 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="R16" s="3" t="n"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
@@ -2927,7 +2904,6 @@
       <c r="R17" s="3" t="n"/>
       <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
-      <c r="U17" s="3" t="n"/>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="n"/>
@@ -2950,7 +2926,6 @@
       <c r="R18" s="3" t="n"/>
       <c r="S18" s="3" t="n"/>
       <c r="T18" s="3" t="n"/>
-      <c r="U18" s="3" t="n"/>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="n"/>
@@ -2973,7 +2948,6 @@
       <c r="R19" s="3" t="n"/>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n"/>
-      <c r="U19" s="3" t="n"/>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="n"/>
@@ -2996,7 +2970,6 @@
       <c r="R20" s="3" t="n"/>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
-      <c r="U20" s="3" t="n"/>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="n"/>
@@ -3019,7 +2992,6 @@
       <c r="R21" s="3" t="n"/>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
-      <c r="U21" s="3" t="n"/>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="n"/>
@@ -3042,7 +3014,6 @@
       <c r="R22" s="3" t="n"/>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n"/>
-      <c r="U22" s="3" t="n"/>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="n"/>
@@ -3065,7 +3036,6 @@
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n"/>
-      <c r="U23" s="3" t="n"/>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="n"/>
@@ -3088,7 +3058,6 @@
       <c r="R24" s="3" t="n"/>
       <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="n"/>
-      <c r="U24" s="3" t="n"/>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="n"/>
@@ -3111,7 +3080,6 @@
       <c r="R25" s="3" t="n"/>
       <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="n"/>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="n"/>
@@ -3134,7 +3102,6 @@
       <c r="R26" s="3" t="n"/>
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n"/>
-      <c r="U26" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3217,7 +3184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3262,78 +3229,106 @@
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Số tiết tối đa một nhóm môn mỗi buổi</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>2</v>
+          <t>Chủ Nhiệm được dạy bù</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Ghép cặp khi nhóm môn có từ (tiết/tuần)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Chủ Nhiệm được dạy bù</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+          <t>Bộ Môn được dạy bù</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Bộ Môn được dạy bù</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Học buổi sáng</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Học buổi chiều</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Tiết HĐTN cố định</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Xếp tiết HĐTN còn lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 2</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Ngày</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Học buổi sáng</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Học buổi chiều</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Tiết HĐTN cố định</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Xếp tiết HĐTN còn lại</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 3</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
         </is>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Thứ 2</t>
+          <t>Thứ 4</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3346,19 +3341,17 @@
           <t>Có</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Thứ 3</t>
+          <t>Thứ 5</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3381,7 +3374,7 @@
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 6</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3391,111 +3384,95 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n"/>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Thứ 5</t>
+          <t>Thứ 7</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Tiết</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Luôn do GVCN dạy</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Hạn chế môn nặng</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>Có</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 6</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 7</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Tiết</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>Luôn do GVCN dạy</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>Hạn chế môn nặng</t>
+      <c r="A17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3506,7 +3483,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3498,7 @@
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -3536,7 +3513,7 @@
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -3551,7 +3528,7 @@
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -3559,36 +3536,6 @@
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
@@ -3605,123 +3552,167 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:W35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="70" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Nhóm</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Kiểu luật</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Với mỗi</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Môn</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gồm môn tăng cường</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Nhãn</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Trừ nhãn</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Khối</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Lớp</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ngày</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Tiết</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Buổi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Giáo viên</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Phép đo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>So sánh</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Số</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Đếm theo</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Môn thứ hai</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Áp dụng khi</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Bắt buộc</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Mức</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Điểm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Luật đọc là</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bảo vệ học sinh</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Nhóm môn, Buổi</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
@@ -3732,18 +3723,56 @@
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
-      <c r="P2" s="3" t="n"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Số tiết</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Tối đa</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="Q2" s="3" t="n"/>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n"/>
+      <c r="V2" s="3" t="n"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, nhóm môn, buổi: mọi tiết: số tiết tối đa 2 (bắt buộc)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="3" t="n"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Bảo vệ học sinh</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Ngày</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Toán</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -3753,38 +3782,112 @@
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
-      <c r="P3" s="3" t="n"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Số tiết</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Tối đa</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q3" s="3" t="n"/>
       <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="n"/>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>&lt;= số ngày</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, ngày: các tiết Toán: số tiết tối đa 1, khi số tiết/tuần &lt;= số ngày (bắt buộc)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Bảo vệ học sinh</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Nhóm môn, Buổi</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Không ghép cặp</t>
+        </is>
+      </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Theo cặp 2 tiết</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="n"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>&gt;= 6, chẵn</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, nhóm môn, buổi: các tiết trừ nhãn Không ghép cặp: thành cặp 2 tiết liền trong buổi, khi số tiết/tuần &gt;= 6, chẵn (bắt buộc)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Bảo vệ học sinh</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Môn</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -3795,20 +3898,52 @@
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Liền nhau</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, môn: mọi tiết: liền nhau trong buổi (bắt buộc)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Bảo vệ học sinh</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Nhóm môn, Ngày</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Môn tăng cường</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
@@ -3816,20 +3951,56 @@
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Thứ tự</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Sau</t>
+        </is>
+      </c>
       <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="n"/>
       <c r="R6" s="3" t="n"/>
       <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, nhóm môn, ngày: các tiết có nhãn Môn tăng cường: đứng sau các tiết môn khác cùng nhóm (bắt buộc)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Bảo vệ học sinh</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Nhóm môn, Ngày</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Môn tăng cường</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
@@ -3837,20 +4008,52 @@
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Đi kèm</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
       <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n"/>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, nhóm môn, ngày: các tiết có nhãn Môn tăng cường: có thì phải có tiết môn khác cùng nhóm (bắt buộc)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN và GVCN</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Giờ học</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Môn HĐTN, Tiết HĐTN cố định</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
@@ -3858,20 +4061,54 @@
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Số tiết</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Đúng</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n"/>
+      <c r="V8" s="3" t="n"/>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, giờ học: các tiết có nhãn Môn HĐTN ở ô có nhãn Tiết HĐTN cố định: số tiết đúng 1 (bắt buộc)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN và GVCN</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Môn HĐTN, Xếp tiết HĐTN còn lại, Tiết HĐTN cố định</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
@@ -3879,54 +4116,1200 @@
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Vị trí</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ trong</t>
+        </is>
+      </c>
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n"/>
       <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Các tiết có nhãn Môn HĐTN: chỉ trong ô có nhãn Xếp tiết HĐTN còn lại hoặc Tiết HĐTN cố định (bắt buộc)</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN và GVCN</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Lớp</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Môn HĐTN, Xếp tiết HĐTN còn lại</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Tiết HĐTN cố định</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Khoảng cách</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Cách cuối buổi tối đa</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" s="3" t="n"/>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp: các tiết có nhãn Môn HĐTN ở ô có nhãn Xếp tiết HĐTN còn lại trừ ô có nhãn Tiết HĐTN cố định: cách cuối buổi tối đa 0 tiết (ưu tiên, 200 điểm)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN và GVCN</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Luôn do GVCN dạy</t>
+        </is>
+      </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Chủ Nhiệm</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Người dạy</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>Do</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="n"/>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Mọi tiết ở ô có nhãn Luôn do GVCN dạy: do Chủ Nhiệm dạy (bắt buộc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN và GVCN</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ GVCN dạy</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Chủ Nhiệm</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Người dạy</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Do</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n"/>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n"/>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Các tiết có nhãn Chỉ GVCN dạy: do Chủ Nhiệm dạy (bắt buộc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Người dạy</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Nhóm môn, Buổi</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Người dạy</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>Liền nhau cùng người</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, nhóm môn, buổi: mọi tiết: hai tiết liền nhau do cùng một người dạy (bắt buộc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Người dạy</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Nhóm môn</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>GVCN nhận trọn</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Chủ Nhiệm</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Người dạy</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>Tiết đầu tuần do</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3" t="n"/>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n"/>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3" t="n"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, nhóm môn: các tiết có nhãn GVCN nhận trọn: tiết đầu tuần do Chủ Nhiệm dạy, tiết của người khác không đứng trước (bắt buộc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Lịch giáo viên</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Buổi nghỉ của giáo viên</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="n"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi giáo viên không dạy ở buổi nghỉ ghi ở cột Buổi Nghỉ, nghỉ đủ số buổi bất kỳ (bắt buộc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lịch giáo viên</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Giáo viên, Buổi</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Số khác nhau</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>Tối đa</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>Cơ sở</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi giáo viên, buổi: mọi tiết: số cơ sở khác nhau tối đa 1 (bắt buộc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="25" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Lịch giáo viên</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Giáo viên, Ngày</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Số khác nhau</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>Tối đa</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>Cơ sở</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi giáo viên, ngày: mọi tiết: số cơ sở khác nhau tối đa 1 (ưu tiên, 10000 điểm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Lịch giáo viên</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Giáo viên chỉ dạy cơ sở 2</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n"/>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n"/>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="n"/>
+      <c r="V18" s="3" t="n"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Giáo viên ghi Cơ sở 2 hoặc Thai Sản (không chủ nhiệm) chỉ dạy các lớp ở cơ sở 2 (bắt buộc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên khi xếp giờ</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Môn nặng, Hạn chế môn nặng</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Vị trí</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>Không trong</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="n"/>
+      <c r="V19" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Các tiết có nhãn Môn nặng: không trong ô có nhãn Hạn chế môn nặng (ưu tiên, 1200 điểm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên khi xếp giờ</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Ưu tiên buổi sáng</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Sáng</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Vị trí</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ trong</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n"/>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="3" t="n"/>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="n"/>
+      <c r="V20" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Các tiết có nhãn Ưu tiên buổi sáng: chỉ trong buổi sáng (ưu tiên, 300 điểm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên khi xếp giờ</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Giáo viên, Ngày</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Số tiết</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>Tối đa</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>tải ngày</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="n"/>
+      <c r="V21" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi giáo viên, ngày: mọi tiết: số tiết tối đa tải ngày (ưu tiên, 100 điểm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên khi xếp giờ</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Giáo viên, Ngày</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Số tiết</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>Tối đa</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>tải ngày + 1</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="n"/>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="n"/>
+      <c r="V22" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi giáo viên, ngày: mọi tiết: số tiết tối đa tải ngày + 1 (ưu tiên, 300 điểm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên khi xếp giờ</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Môn, Ngày</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Môn HĐTN, Ưu tiên buổi sáng</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Số tiết</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>Tối đa</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>số tiết/tuần chia số ngày</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="n"/>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n"/>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, môn, ngày: các tiết trừ nhãn Môn HĐTN, Ưu tiên buổi sáng: số tiết tối đa số tiết/tuần chia số ngày (ưu tiên, 40 điểm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên khi xếp giờ</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Lớp, Môn, Ngày</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Ưu tiên buổi sáng</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Môn HĐTN</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Số tiết</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>Tối đa</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>số tiết/tuần chia số ngày</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="n"/>
+      <c r="R24" s="3" t="n"/>
+      <c r="S24" s="3" t="n"/>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="n"/>
+      <c r="V24" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi lớp, môn, ngày: các tiết có nhãn Ưu tiên buổi sáng trừ nhãn Môn HĐTN: số tiết tối đa số tiết/tuần chia số ngày (ưu tiên, 120 điểm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Ưu tiên khi xếp giờ</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Tự ghép</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Giáo viên, Buổi</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>trừ Chủ Nhiệm</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Khoảng cách</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>Tiết trống tối đa</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3" t="n"/>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="n"/>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="n"/>
+      <c r="V25" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Với mỗi giáo viên, buổi: mọi tiết của GV trừ Chủ Nhiệm: tối đa 0 tiết trống giữa các tiết (ưu tiên, 10 điểm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25" customHeight="1">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
+      <c r="O26" s="3" t="n"/>
+      <c r="P26" s="3" t="n"/>
+      <c r="Q26" s="3" t="n"/>
+      <c r="R26" s="3" t="n"/>
+      <c r="S26" s="3" t="n"/>
+      <c r="T26" s="3" t="n"/>
+      <c r="U26" s="3" t="n"/>
+      <c r="V26" s="3" t="n"/>
+      <c r="W26" s="2" t="n"/>
+    </row>
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="n"/>
+      <c r="S27" s="3" t="n"/>
+      <c r="T27" s="3" t="n"/>
+      <c r="U27" s="3" t="n"/>
+      <c r="V27" s="3" t="n"/>
+      <c r="W27" s="2" t="n"/>
+    </row>
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3" t="n"/>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="n"/>
+      <c r="Q28" s="3" t="n"/>
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" s="3" t="n"/>
+      <c r="T28" s="3" t="n"/>
+      <c r="U28" s="3" t="n"/>
+      <c r="V28" s="3" t="n"/>
+      <c r="W28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="n"/>
+      <c r="O29" s="3" t="n"/>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n"/>
+      <c r="R29" s="3" t="n"/>
+      <c r="S29" s="3" t="n"/>
+      <c r="T29" s="3" t="n"/>
+      <c r="U29" s="3" t="n"/>
+      <c r="V29" s="3" t="n"/>
+      <c r="W29" s="2" t="n"/>
+    </row>
+    <row r="30" ht="25" customHeight="1">
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="3" t="n"/>
+      <c r="O30" s="3" t="n"/>
+      <c r="P30" s="3" t="n"/>
+      <c r="Q30" s="3" t="n"/>
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" s="3" t="n"/>
+      <c r="T30" s="3" t="n"/>
+      <c r="U30" s="3" t="n"/>
+      <c r="V30" s="3" t="n"/>
+      <c r="W30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="25" customHeight="1">
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n"/>
+      <c r="P31" s="3" t="n"/>
+      <c r="Q31" s="3" t="n"/>
+      <c r="R31" s="3" t="n"/>
+      <c r="S31" s="3" t="n"/>
+      <c r="T31" s="3" t="n"/>
+      <c r="U31" s="3" t="n"/>
+      <c r="V31" s="3" t="n"/>
+      <c r="W31" s="2" t="n"/>
+    </row>
+    <row r="32" ht="25" customHeight="1">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3" t="n"/>
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="3" t="n"/>
+      <c r="Q32" s="3" t="n"/>
+      <c r="R32" s="3" t="n"/>
+      <c r="S32" s="3" t="n"/>
+      <c r="T32" s="3" t="n"/>
+      <c r="U32" s="3" t="n"/>
+      <c r="V32" s="3" t="n"/>
+      <c r="W32" s="2" t="n"/>
+    </row>
+    <row r="33" ht="25" customHeight="1">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="n"/>
+      <c r="P33" s="3" t="n"/>
+      <c r="Q33" s="3" t="n"/>
+      <c r="R33" s="3" t="n"/>
+      <c r="S33" s="3" t="n"/>
+      <c r="T33" s="3" t="n"/>
+      <c r="U33" s="3" t="n"/>
+      <c r="V33" s="3" t="n"/>
+      <c r="W33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="25" customHeight="1">
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="3" t="n"/>
+      <c r="Q34" s="3" t="n"/>
+      <c r="R34" s="3" t="n"/>
+      <c r="S34" s="3" t="n"/>
+      <c r="T34" s="3" t="n"/>
+      <c r="U34" s="3" t="n"/>
+      <c r="V34" s="3" t="n"/>
+      <c r="W34" s="2" t="n"/>
+    </row>
+    <row r="35" ht="25" customHeight="1">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="n"/>
+      <c r="P35" s="3" t="n"/>
+      <c r="Q35" s="3" t="n"/>
+      <c r="R35" s="3" t="n"/>
+      <c r="S35" s="3" t="n"/>
+      <c r="T35" s="3" t="n"/>
+      <c r="U35" s="3" t="n"/>
+      <c r="V35" s="3" t="n"/>
+      <c r="W35" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3939,7 +5322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4249,490 +5632,502 @@
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Tối đa tiết mỗi ngày</t>
+          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng, vd Toán: 1; chỉ áp dụng khi số tiết/tuần của môn không quá số ngày học.</t>
+          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
+          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
+          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
+          <t>QUY ĐỊNH: Số tiết buổi sáng</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
+          <t>Buổi sáng là tiết 1 đến tiết này.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Số tiết buổi sáng</t>
+          <t>QUY ĐỊNH: Số tiết buổi chiều</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Buổi sáng là tiết 1 đến tiết này.</t>
+          <t>Buổi chiều là các tiết tiếp theo, vd sáng 4 tiết, chiều 3 tiết thì chiều là tiết 5, 6, 7.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Số tiết buổi chiều</t>
+          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Buổi chiều là các tiết tiếp theo, vd sáng 4 tiết, chiều 3 tiết thì chiều là tiết 5, 6, 7.</t>
+          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Số tiết tối đa một nhóm môn mỗi buổi</t>
+          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng; môn có từ 2 tiết trong một buổi thì các tiết đó phải liền nhau.</t>
+          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Ghép cặp khi nhóm môn có từ (tiết/tuần)</t>
+          <t>QUY ĐỊNH: Học buổi sáng</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: nhóm môn có từ ngần ấy tiết/tuần và tổng số tiết chẵn thì xếp thành các cặp 2 tiết liền, cùng người dạy (trừ môn ghi Có ở cột Không ghép cặp).</t>
+          <t>Các ngày học, liền nhau từ Thứ 2 (có thể thêm Thứ 7).</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
+          <t>QUY ĐỊNH: Học buổi chiều</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
+          <t>Ngày có buổi chiều (phải là ngày học buổi sáng).</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
+          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
+          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Học buổi sáng</t>
+          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Các ngày học, liền nhau từ Thứ 2 (có thể thêm Thứ 7).</t>
+          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Học buổi chiều</t>
+          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Ngày có buổi chiều (phải là ngày học buổi sáng).</t>
+          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
+          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
+          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
+          <t>CHỨC VỤ</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
+          <t>LUẬT</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật, thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Điểm (điểm trừ mỗi lần không theo) hoặc Mức 1, 2, 3 (100, 400, 1500 điểm). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của ngày, tiết (vd Luôn do GVCN dạy); nhiều nhãn ô là ô có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
+          <t>LUẬT: Không xếp vào</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+          <t>Môn (của các khối ở cột Khối; trống: mọi khối) không học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không học tiết 1; Tin học không học Thứ 2.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CHỨC VỤ</t>
+          <t>LUẬT: Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
+          <t>Môn chỉ học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ học buổi chiều.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG</t>
+          <t>LUẬT: Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một luật riêng của trường: chọn Kiểu luật (một mẫu, hoặc Tự ghép) rồi ghi các cột kiểu đó dùng (cột không dùng để trống). Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên, ô trống là Không); Mức: 1, 2, 3 (chỉ cho luật ưu tiên, trống là 2, 3 là ưu tiên nhất). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt, vd Tiếng Anh). Nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của ngày, tiết (vd Luôn do GVCN dạy). Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (cả môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Không xếp vào</t>
+          <t>LUẬT: Học trước</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; trống: mọi khối) không học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không học tiết 1; Tin học không học Thứ 2.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Chỉ xếp vào</t>
+          <t>LUẬT: Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ học buổi chiều.</t>
+          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Học 2 tiết liền</t>
+          <t>LUẬT: Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (cả môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Môn có tối đa Số lớp học cùng một tiết (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Học trước</t>
+          <t>LUẬT: Cố định vào</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi tiết ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT: Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một tiết (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Cố định vào</t>
+          <t>LUẬT: Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi tiết ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định Thứ 3 tiết 3.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên có chức vụ ở cột Giáo viên dạy, vd Tin học khối 3 chỉ Tin Học dạy; tiết 1 Thứ 2 chỉ Chủ Nhiệm dạy.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Giáo viên không dạy ở các buổi nghỉ cố định ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi bất kỳ ghi ở cột đó. Chỉ ghi Bắt buộc = Có; xóa dòng là bỏ luật.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Học ít nhất số ngày</t>
+          <t>LUẬT: Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; xóa dòng là bỏ luật.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Chỉ giáo viên dạy</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên có chức vụ ở cột Giáo viên dạy, vd Tin học khối 3 chỉ Tin Học dạy; tiết 1 Thứ 2 chỉ Chủ Nhiệm dạy.</t>
+          <t>Ghép câu luật: Với mỗi [phạm vi], các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] thì [Phép đo] [So sánh] [Số], khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Ghép câu luật: Với mỗi [phạm vi], các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] thì [Phép đo] [So sánh] [Số], khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày tối đa 1 tiết Toán; mỗi giờ học tối đa 1 lớp Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày tối đa 1 tiết Toán; mỗi giờ học tối đa 1 lớp Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Số giá trị khác nhau ở cột Đếm theo, vd mỗi GV mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Số giá trị khác nhau ở cột Đếm theo, vd mỗi GV mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Các tiết chỉ nằm trong / không nằm trong các ngày, tiết, buổi (và nhãn ngày, tiết) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ nằm trong / không nằm trong các ngày, tiết, buổi (và nhãn ngày, tiết) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Các tiết trong mỗi buổi (của mỗi lớp hoặc GV) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong mỗi buổi (của mỗi lớp hoặc GV) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Mỗi buổi 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: không có tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: không có tiết lẻ đứng một mình).</t>
+          <t>Trong mỗi buổi (hoặc ngày, nếu phạm vi có Ngày) các tiết ở cột Môn đứng trước (hoặc sau) các tiết Môn thứ hai. Môn thứ hai trống và phạm vi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Trong mỗi buổi (hoặc ngày, nếu phạm vi có Ngày) các tiết ở cột Môn đứng trước các tiết Môn thứ hai. Ghi cột Môn thứ hai.</t>
+          <t>Buổi (hoặc ngày) có tiết ở cột Môn thì cũng có tiết Môn thứ hai. Môn thứ hai trống và phạm vi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết ở cột Môn thì cũng có tiết Môn thứ hai. Ghi cột Môn thứ hai.</t>
+          <t>Các tiết do GV có chức vụ ở cột Giáo viên dạy; hoặc mọi tiết trong mỗi phạm vi do cùng một người; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do GV có chức vụ ở cột Giáo viên dạy và tiết của người khác không đứng trước tiết đó. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do GV có chức vụ ở cột Giáo viên dạy; hoặc mọi tiết trong mỗi phạm vi do cùng một người. So sánh: Do, Cùng một người.</t>
+          <t>Số tiết trống giữa các tiết trong buổi tối đa ngần ấy; hoặc mỗi tiết cách cuối buổi tối đa ngần ấy tiết. So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống giữa các tiết trong buổi tối đa ngần ấy; hoặc mỗi tiết cách cuối buổi tối đa ngần ấy tiết. So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LUẬT RIÊNG: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng cho khối mà số tiết/tuần của các môn ở cột Môn thỏa điều kiện, vd '&gt;= 6, chẵn' hoặc '&lt;= số ngày'.</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' hoặc '&lt;= số ngày'.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="25" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -3748,7 +3748,7 @@
       <c r="V2" s="3" t="n"/>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, nhóm môn, buổi: mọi tiết: số tiết tối đa 2 (bắt buộc)</t>
+          <t>Mỗi buổi, một lớp học tối đa 2 tiết của một môn, tính chung môn chính với môn tăng cường cùng nhóm (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       <c r="V3" s="3" t="n"/>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, ngày: các tiết Toán: số tiết tối đa 1, khi số tiết/tuần &lt;= số ngày (bắt buộc)</t>
+          <t>Mỗi ngày, một lớp học tối đa 1 tiết Toán, khi số tiết/tuần của môn không quá số ngày học (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       <c r="V4" s="3" t="n"/>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, nhóm môn, buổi: các tiết trừ nhãn Không ghép cặp: thành cặp 2 tiết liền trong buổi, khi số tiết/tuần &gt;= 6, chẵn (bắt buộc)</t>
+          <t>Môn có từ 6 tiết/tuần trở lên và số tiết chẵn, tính chung môn tăng cường cùng nhóm, học thành cặp 2 tiết liền trong buổi; trừ môn có nhãn Không ghép cặp (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       <c r="V5" s="3" t="n"/>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, môn: mọi tiết: liền nhau trong buổi (bắt buộc)</t>
+          <t>Các tiết của một môn trong cùng buổi phải đứng liền nhau (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       <c r="V6" s="3" t="n"/>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, nhóm môn, ngày: các tiết có nhãn Môn tăng cường: đứng sau các tiết môn khác cùng nhóm (bắt buộc)</t>
+          <t>Trong một ngày, tiết môn tăng cường đứng sau các tiết môn chính cùng nhóm (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       <c r="V7" s="3" t="n"/>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, nhóm môn, ngày: các tiết có nhãn Môn tăng cường: có thì phải có tiết môn khác cùng nhóm (bắt buộc)</t>
+          <t>Ngày có tiết môn tăng cường thì cũng có tiết môn chính cùng nhóm (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       <c r="V8" s="3" t="n"/>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, giờ học: các tiết có nhãn Môn HĐTN ở ô có nhãn Tiết HĐTN cố định: số tiết đúng 1 (bắt buộc)</t>
+          <t>Ở mỗi giờ có nhãn Tiết HĐTN cố định, mỗi lớp học đúng 1 tiết HĐTN (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
       <c r="V9" s="3" t="n"/>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>Các tiết có nhãn Môn HĐTN: chỉ trong ô có nhãn Xếp tiết HĐTN còn lại hoặc Tiết HĐTN cố định (bắt buộc)</t>
+          <t>Tiết HĐTN chỉ xếp vào giờ có nhãn Tiết HĐTN cố định hoặc Xếp tiết HĐTN còn lại (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp: các tiết có nhãn Môn HĐTN ở ô có nhãn Xếp tiết HĐTN còn lại trừ ô có nhãn Tiết HĐTN cố định: cách cuối buổi tối đa 0 tiết (ưu tiên, 200 điểm)</t>
+          <t>Tiết HĐTN còn lại, ngoài giờ cố định, xếp ở tiết cuối buổi (ưu tiên thấp)</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       <c r="V11" s="3" t="n"/>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>Mọi tiết ở ô có nhãn Luôn do GVCN dạy: do Chủ Nhiệm dạy (bắt buộc)</t>
+          <t>Ở giờ có nhãn Luôn do GVCN dạy, lớp học với GV chủ nhiệm (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       <c r="V12" s="3" t="n"/>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>Các tiết có nhãn Chỉ GVCN dạy: do Chủ Nhiệm dạy (bắt buộc)</t>
+          <t>Môn có nhãn Chỉ GVCN dạy thì chỉ GV chủ nhiệm dạy (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       <c r="V13" s="3" t="n"/>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, nhóm môn, buổi: mọi tiết: hai tiết liền nhau do cùng một người dạy (bắt buộc)</t>
+          <t>Hai tiết liền nhau của một môn (cùng nhóm) trong buổi do cùng một giáo viên dạy (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       <c r="V14" s="3" t="n"/>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, nhóm môn: các tiết có nhãn GVCN nhận trọn: tiết đầu tuần do Chủ Nhiệm dạy, tiết của người khác không đứng trước (bắt buộc)</t>
+          <t>Môn có nhãn GVCN nhận trọn: tiết đầu tuần của lớp do GV chủ nhiệm dạy, tiết của giáo viên khác không đứng trước (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       <c r="V15" s="3" t="n"/>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên không dạy ở buổi nghỉ ghi ở cột Buổi Nghỉ, nghỉ đủ số buổi bất kỳ (bắt buộc)</t>
+          <t>Giáo viên không dạy vào buổi nghỉ ghi ở cột Buổi Nghỉ và nghỉ đủ số buổi ghi ở đó (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       <c r="V16" s="3" t="n"/>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi giáo viên, buổi: mọi tiết: số cơ sở khác nhau tối đa 1 (bắt buộc)</t>
+          <t>Mỗi buổi, một giáo viên chỉ dạy ở một cơ sở (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi giáo viên, ngày: mọi tiết: số cơ sở khác nhau tối đa 1 (ưu tiên, 10000 điểm)</t>
+          <t>Hạn chế để một giáo viên dạy ở cả hai cơ sở trong cùng một ngày (ưu tiên rất cao)</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       <c r="V18" s="3" t="n"/>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên ghi Cơ sở 2 hoặc Thai Sản (không chủ nhiệm) chỉ dạy các lớp ở cơ sở 2 (bắt buộc)</t>
+          <t>Giáo viên không chủ nhiệm ghi Cơ sở 2 hoặc Thai Sản chỉ dạy các lớp ở cơ sở 2 (bắt buộc)</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>Các tiết có nhãn Môn nặng: không trong ô có nhãn Hạn chế môn nặng (ưu tiên, 1200 điểm)</t>
+          <t>Tránh xếp môn có nhãn Môn nặng vào giờ có nhãn Hạn chế môn nặng (ưu tiên cao)</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>Các tiết có nhãn Ưu tiên buổi sáng: chỉ trong buổi sáng (ưu tiên, 300 điểm)</t>
+          <t>Môn có nhãn Ưu tiên buổi sáng xếp vào buổi sáng (ưu tiên vừa)</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi giáo viên, ngày: mọi tiết: số tiết tối đa tải ngày (ưu tiên, 100 điểm)</t>
+          <t>Số tiết mỗi ngày của giáo viên không quá tải ngày, tức số tiết/tuần chia đều cho các ngày (ưu tiên thấp)</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi giáo viên, ngày: mọi tiết: số tiết tối đa tải ngày + 1 (ưu tiên, 300 điểm)</t>
+          <t>Số tiết mỗi ngày của giáo viên không quá tải ngày + 1 tiết (ưu tiên vừa)</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, môn, ngày: các tiết trừ nhãn Môn HĐTN, Ưu tiên buổi sáng: số tiết tối đa số tiết/tuần chia số ngày (ưu tiên, 40 điểm)</t>
+          <t>Mỗi môn, trừ HĐTN và môn ưu tiên buổi sáng, rải đều trong tuần: một ngày không quá số tiết/tuần chia số ngày (ưu tiên thấp)</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi lớp, môn, ngày: các tiết có nhãn Ưu tiên buổi sáng trừ nhãn Môn HĐTN: số tiết tối đa số tiết/tuần chia số ngày (ưu tiên, 120 điểm)</t>
+          <t>Môn ưu tiên buổi sáng rải đều trong tuần: một ngày không quá số tiết/tuần chia số ngày (ưu tiên thấp)</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>Với mỗi giáo viên, buổi: mọi tiết của GV trừ Chủ Nhiệm: tối đa 0 tiết trống giữa các tiết (ưu tiên, 10 điểm)</t>
+          <t>Giáo viên, trừ GV chủ nhiệm, không có tiết trống xen giữa các tiết trong buổi (ưu tiên thấp)</t>
         </is>
       </c>
     </row>
@@ -5805,151 +5805,151 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật, thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Điểm (điểm trừ mỗi lần không theo) hoặc Mức 1, 2, 3 (100, 400, 1500 điểm). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của ngày, tiết (vd Luôn do GVCN dạy); nhiều nhãn ô là ô có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật, thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Không xếp vào</t>
+          <t>LUẬT: Ở đâu · Không xếp vào</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; trống: mọi khối) không học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không học tiết 1; Tin học không học Thứ 2.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Chỉ xếp vào</t>
+          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ học vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ học buổi chiều.</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Học 2 tiết liền</t>
+          <t>LUẬT: Ở đâu · Cố định vào</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (cả môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Học trước</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một tiết (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Cố định vào</t>
+          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi tiết ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định Thứ 3 tiết 3.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Học ít nhất số ngày</t>
+          <t>LUẬT: Đi cùng nhau · Học trước</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Chỉ giáo viên dạy</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên có chức vụ ở cột Giáo viên dạy, vd Tin học khối 3 chỉ Tin Học dạy; tiết 1 Thứ 2 chỉ Chủ Nhiệm dạy.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên có chức vụ ở cột Giáo viên dạy, vd Tin học khối 3 chỉ GV Tin Học dạy; tiết 1 Thứ 2 chỉ GV chủ nhiệm dạy.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy ở các buổi nghỉ cố định ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi bất kỳ ghi ở cột đó. Chỉ ghi Bắt buộc = Có; xóa dòng là bỏ luật.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; xóa dòng là bỏ luật.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng.</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Ghép câu luật: Với mỗi [phạm vi], các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] thì [Phép đo] [So sánh] [Số], khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
@@ -5980,108 +5980,108 @@
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày tối đa 1 tiết Toán; mỗi giờ học tối đa 1 lớp Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Số giá trị khác nhau ở cột Đếm theo, vd mỗi GV mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ nằm trong / không nằm trong các ngày, tiết, buổi (và nhãn ngày, tiết) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong mỗi buổi (của mỗi lớp hoặc GV) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: không có tiết lẻ đứng một mình).</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Trong mỗi buổi (hoặc ngày, nếu phạm vi có Ngày) các tiết ở cột Môn đứng trước (hoặc sau) các tiết Môn thứ hai. Môn thứ hai trống và phạm vi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết ở cột Môn thì cũng có tiết Môn thứ hai. Môn thứ hai trống và phạm vi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do GV có chức vụ ở cột Giáo viên dạy; hoặc mọi tiết trong mỗi phạm vi do cùng một người; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do GV có chức vụ ở cột Giáo viên dạy và tiết của người khác không đứng trước tiết đó. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống giữa các tiết trong buổi tối đa ngần ấy; hoặc mỗi tiết cách cuối buổi tối đa ngần ấy tiết. So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Các tiết do giáo viên có chức vụ ở cột Giáo viên dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do chức vụ đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' hoặc '&lt;= số ngày'.</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
         </is>
       </c>
     </row>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -5805,7 +5805,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật, thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật, thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều.</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên có chức vụ ở cột Giáo viên (để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên có chức vụ ở cột Giáo viên dạy, vd Tin học khối 3 chỉ GV Tin Học dạy; tiết 1 Thứ 2 chỉ GV chủ nhiệm dạy.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên có chức vụ ở cột Giáo viên dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do chức vụ đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -3552,7 +3552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3693,6 +3693,11 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>Tạm tắt</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>Luật đọc là</t>
         </is>
       </c>
@@ -3746,7 +3751,8 @@
       </c>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W2" s="3" t="n"/>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Mỗi buổi, một lớp học tối đa 2 tiết của một môn, tính chung môn chính với môn tăng cường cùng nhóm (bắt buộc)</t>
         </is>
@@ -3809,7 +3815,8 @@
       </c>
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="W3" s="3" t="n"/>
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>Mỗi ngày, một lớp học tối đa 1 tiết Toán, khi số tiết/tuần của môn không quá số ngày học (bắt buộc)</t>
         </is>
@@ -3866,7 +3873,8 @@
       </c>
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Môn có từ 6 tiết/tuần trở lên và số tiết chẵn, tính chung môn tăng cường cùng nhóm, học thành cặp 2 tiết liền trong buổi; trừ môn có nhãn Không ghép cặp (bắt buộc)</t>
         </is>
@@ -3915,7 +3923,8 @@
       </c>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>Các tiết của một môn trong cùng buổi phải đứng liền nhau (bắt buộc)</t>
         </is>
@@ -3972,7 +3981,8 @@
       </c>
       <c r="U6" s="3" t="n"/>
       <c r="V6" s="3" t="n"/>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>Trong một ngày, tiết môn tăng cường đứng sau các tiết môn chính cùng nhóm (bắt buộc)</t>
         </is>
@@ -4025,7 +4035,8 @@
       </c>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="W7" s="3" t="n"/>
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>Ngày có tiết môn tăng cường thì cũng có tiết môn chính cùng nhóm (bắt buộc)</t>
         </is>
@@ -4084,7 +4095,8 @@
       </c>
       <c r="U8" s="3" t="n"/>
       <c r="V8" s="3" t="n"/>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="W8" s="3" t="n"/>
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>Ở mỗi giờ có nhãn Tiết HĐTN cố định, mỗi lớp học đúng 1 tiết HĐTN (bắt buộc)</t>
         </is>
@@ -4137,7 +4149,8 @@
       </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n"/>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="W9" s="3" t="n"/>
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>Tiết HĐTN chỉ xếp vào giờ có nhãn Tiết HĐTN cố định hoặc Xếp tiết HĐTN còn lại (bắt buộc)</t>
         </is>
@@ -4202,7 +4215,8 @@
       <c r="V10" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="W10" s="3" t="n"/>
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>Tiết HĐTN còn lại, ngoài giờ cố định, xếp ở tiết cuối buổi (ưu tiên thấp)</t>
         </is>
@@ -4259,7 +4273,8 @@
       </c>
       <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
-      <c r="W11" s="2" t="inlineStr">
+      <c r="W11" s="3" t="n"/>
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>Ở giờ có nhãn Luôn do GVCN dạy, lớp học với GV chủ nhiệm (bắt buộc)</t>
         </is>
@@ -4316,7 +4331,8 @@
       </c>
       <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="n"/>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="W12" s="3" t="n"/>
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>Môn có nhãn Chỉ GVCN dạy thì chỉ GV chủ nhiệm dạy (bắt buộc)</t>
         </is>
@@ -4369,7 +4385,8 @@
       </c>
       <c r="U13" s="3" t="n"/>
       <c r="V13" s="3" t="n"/>
-      <c r="W13" s="2" t="inlineStr">
+      <c r="W13" s="3" t="n"/>
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>Hai tiết liền nhau của một môn (cùng nhóm) trong buổi do cùng một giáo viên dạy (bắt buộc)</t>
         </is>
@@ -4430,7 +4447,8 @@
       </c>
       <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n"/>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="W14" s="3" t="n"/>
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>Môn có nhãn GVCN nhận trọn: tiết đầu tuần của lớp do GV chủ nhiệm dạy, tiết của giáo viên khác không đứng trước (bắt buộc)</t>
         </is>
@@ -4471,7 +4489,8 @@
       </c>
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="3" t="n"/>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="W15" s="3" t="n"/>
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>Giáo viên không dạy vào buổi nghỉ ghi ở cột Buổi Nghỉ và nghỉ đủ số buổi ghi ở đó (bắt buộc)</t>
         </is>
@@ -4530,7 +4549,8 @@
       </c>
       <c r="U16" s="3" t="n"/>
       <c r="V16" s="3" t="n"/>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>Mỗi buổi, một giáo viên chỉ dạy ở một cơ sở (bắt buộc)</t>
         </is>
@@ -4591,7 +4611,8 @@
       <c r="V17" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W17" s="3" t="n"/>
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>Hạn chế để một giáo viên dạy ở cả hai cơ sở trong cùng một ngày (ưu tiên rất cao)</t>
         </is>
@@ -4632,7 +4653,8 @@
       </c>
       <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="n"/>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="W18" s="3" t="n"/>
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>Giáo viên không chủ nhiệm ghi Cơ sở 2 hoặc Thai Sản chỉ dạy các lớp ở cơ sở 2 (bắt buộc)</t>
         </is>
@@ -4687,7 +4709,8 @@
       <c r="V19" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="W19" s="3" t="n"/>
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>Tránh xếp môn có nhãn Môn nặng vào giờ có nhãn Hạn chế môn nặng (ưu tiên cao)</t>
         </is>
@@ -4746,7 +4769,8 @@
       <c r="V20" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="W20" s="3" t="n"/>
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>Môn có nhãn Ưu tiên buổi sáng xếp vào buổi sáng (ưu tiên vừa)</t>
         </is>
@@ -4805,7 +4829,8 @@
       <c r="V21" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="W21" s="2" t="inlineStr">
+      <c r="W21" s="3" t="n"/>
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>Số tiết mỗi ngày của giáo viên không quá tải ngày, tức số tiết/tuần chia đều cho các ngày (ưu tiên thấp)</t>
         </is>
@@ -4864,7 +4889,8 @@
       <c r="V22" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="W22" s="3" t="n"/>
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>Số tiết mỗi ngày của giáo viên không quá tải ngày + 1 tiết (ưu tiên vừa)</t>
         </is>
@@ -4927,7 +4953,8 @@
       <c r="V23" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="W23" s="3" t="n"/>
+      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>Mỗi môn, trừ HĐTN và môn ưu tiên buổi sáng, rải đều trong tuần: một ngày không quá số tiết/tuần chia số ngày (ưu tiên thấp)</t>
         </is>
@@ -4994,7 +5021,8 @@
       <c r="V24" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="W24" s="3" t="n"/>
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>Môn ưu tiên buổi sáng rải đều trong tuần: một ngày không quá số tiết/tuần chia số ngày (ưu tiên thấp)</t>
         </is>
@@ -5055,7 +5083,8 @@
       <c r="V25" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="W25" s="3" t="n"/>
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>Giáo viên, trừ GV chủ nhiệm, không có tiết trống xen giữa các tiết trong buổi (ưu tiên thấp)</t>
         </is>
@@ -5084,7 +5113,8 @@
       <c r="T26" s="3" t="n"/>
       <c r="U26" s="3" t="n"/>
       <c r="V26" s="3" t="n"/>
-      <c r="W26" s="2" t="n"/>
+      <c r="W26" s="3" t="n"/>
+      <c r="X26" s="2" t="n"/>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="n"/>
@@ -5109,7 +5139,8 @@
       <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="n"/>
       <c r="V27" s="3" t="n"/>
-      <c r="W27" s="2" t="n"/>
+      <c r="W27" s="3" t="n"/>
+      <c r="X27" s="2" t="n"/>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="n"/>
@@ -5134,7 +5165,8 @@
       <c r="T28" s="3" t="n"/>
       <c r="U28" s="3" t="n"/>
       <c r="V28" s="3" t="n"/>
-      <c r="W28" s="2" t="n"/>
+      <c r="W28" s="3" t="n"/>
+      <c r="X28" s="2" t="n"/>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="n"/>
@@ -5159,7 +5191,8 @@
       <c r="T29" s="3" t="n"/>
       <c r="U29" s="3" t="n"/>
       <c r="V29" s="3" t="n"/>
-      <c r="W29" s="2" t="n"/>
+      <c r="W29" s="3" t="n"/>
+      <c r="X29" s="2" t="n"/>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="n"/>
@@ -5184,7 +5217,8 @@
       <c r="T30" s="3" t="n"/>
       <c r="U30" s="3" t="n"/>
       <c r="V30" s="3" t="n"/>
-      <c r="W30" s="2" t="n"/>
+      <c r="W30" s="3" t="n"/>
+      <c r="X30" s="2" t="n"/>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="n"/>
@@ -5209,7 +5243,8 @@
       <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n"/>
       <c r="V31" s="3" t="n"/>
-      <c r="W31" s="2" t="n"/>
+      <c r="W31" s="3" t="n"/>
+      <c r="X31" s="2" t="n"/>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="n"/>
@@ -5234,7 +5269,8 @@
       <c r="T32" s="3" t="n"/>
       <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="n"/>
-      <c r="W32" s="2" t="n"/>
+      <c r="W32" s="3" t="n"/>
+      <c r="X32" s="2" t="n"/>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="n"/>
@@ -5259,7 +5295,8 @@
       <c r="T33" s="3" t="n"/>
       <c r="U33" s="3" t="n"/>
       <c r="V33" s="3" t="n"/>
-      <c r="W33" s="2" t="n"/>
+      <c r="W33" s="3" t="n"/>
+      <c r="X33" s="2" t="n"/>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="n"/>
@@ -5284,7 +5321,8 @@
       <c r="T34" s="3" t="n"/>
       <c r="U34" s="3" t="n"/>
       <c r="V34" s="3" t="n"/>
-      <c r="W34" s="2" t="n"/>
+      <c r="W34" s="3" t="n"/>
+      <c r="X34" s="2" t="n"/>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="n"/>
@@ -5309,7 +5347,8 @@
       <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="n"/>
       <c r="V35" s="3" t="n"/>
-      <c r="W35" s="2" t="n"/>
+      <c r="W35" s="3" t="n"/>
+      <c r="X35" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5805,7 +5844,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật, thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5976,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5988,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NHÂN SỰ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CHƯƠNG TRÌNH HỌC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CHỨC VỤ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="QUY ĐỊNH" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="LUẬT" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="HƯỚNG DẪN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NHÂN SỰ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHƯƠNG TRÌNH HỌC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHỨC VỤ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUY ĐỊNH" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LUẬT" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HƯỚNG DẪN" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3184,7 +3184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3209,114 +3209,124 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Số tiết buổi sáng</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>4</v>
+          <t>Chủ Nhiệm được dạy bù</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Số tiết buổi chiều</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+          <t>Bộ Môn được dạy bù</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Buổi Sáng</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Buổi Chiều</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Tiết HĐTN cố định</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Xếp tiết HĐTN còn lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 2</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Chủ Nhiệm được dạy bù</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Thứ 3</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Bộ Môn được dạy bù</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Ngày</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Học buổi sáng</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Học buổi chiều</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Tiết HĐTN cố định</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Xếp tiết HĐTN còn lại</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Thứ 2</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Có</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Thứ 3</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
+          <t>Thứ 5</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="inlineStr">
@@ -3328,121 +3338,91 @@
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Tiết</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Luôn do GVCN dạy</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Hạn chế môn nặng</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="25" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 5</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 6</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Thứ 7</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="inlineStr">
+    </row>
+    <row r="14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Không</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Tiết</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Luôn do GVCN dạy</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>Hạn chế môn nặng</t>
+      <c r="A15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Không</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3453,7 +3433,7 @@
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -3468,7 +3448,7 @@
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -3483,7 +3463,7 @@
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -3491,51 +3471,6 @@
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
@@ -5361,7 +5296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5496,7 +5431,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Buổi không xếp tiết: buổi cố định (vd Chiều T5, Sáng T6) hoặc số buổi bất kỳ (vd 2 buổi chiều), cách nhau bằng dấu phẩy. GVCN không nghỉ buổi sáng được (tiết Luôn do GVCN dạy ở sheet QUY ĐỊNH).</t>
+          <t>Buổi không xếp tiết: buổi cố định (vd Chiều T5, Sáng T6) hoặc số buổi bất kỳ (vd 2 buổi chiều), cách nhau bằng dấu phẩy. GVCN không nghỉ được buổi có tiết Luôn do GVCN dạy (sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5467,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (Thứ 2 … Thứ 7); Tiết (buổi chiều đánh số nối tiếp buổi sáng, sáng 4 tiết thì chiều từ tiết 5; thêm tiết thì thêm dòng).</t>
+          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
         </is>
       </c>
     </row>
@@ -5707,466 +5642,430 @@
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Số tiết buổi sáng</t>
+          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Buổi sáng là tiết 1 đến tiết này.</t>
+          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Số tiết buổi chiều</t>
+          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Buổi chiều là các tiết tiếp theo, vd sáng 4 tiết, chiều 3 tiết thì chiều là tiết 5, 6, 7.</t>
+          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
+          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
+          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
+          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
+          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Học buổi sáng</t>
+          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Các ngày học, liền nhau từ Thứ 2 (có thể thêm Thứ 7).</t>
+          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Học buổi chiều</t>
+          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Ngày có buổi chiều (phải là ngày học buổi sáng).</t>
+          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
+          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
+          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
+          <t>CHỨC VỤ</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
+          <t>LUẬT</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
+          <t>LUẬT: Ở đâu · Không xếp vào</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CHỨC VỤ</t>
+          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LUẬT</t>
+          <t>LUẬT: Ở đâu · Cố định vào</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Không xếp vào</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Cố định vào</t>
+          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
+          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Đi cùng nhau · Học trước</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học trước</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: cấu trúc của TKB</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>Kiểu chữ</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="25" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="25" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>LUẬT: cấu trúc của TKB</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="25" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Kiểu chữ</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NHÂN SỰ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHƯƠNG TRÌNH HỌC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHỨC VỤ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUY ĐỊNH" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LUẬT" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HƯỚNG DẪN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LỚP" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHỨC VỤ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUY ĐỊNH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LUẬT" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HƯỚNG DẪN" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -68,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -83,6 +84,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3114,6 +3118,959 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C300"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lớp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Khối</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cơ sở 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="5" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="5" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="5" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="5" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="5" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="5" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="5" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="5" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="5" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="5" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="5" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="5" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="5" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="5" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="5" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="5" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="5" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="5" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="5" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="5" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="5" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="5" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="5" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="5" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="5" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="5" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="5" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="5" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3178,7 +4135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3481,7 +4438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5290,13 +6247,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5359,7 +6316,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chỉ ghi cho Chủ Nhiệm, dạng khối/số thứ tự (vd 1/1) hoặc khối rồi tên lớp (vd 1D15). Mỗi lớp một Chủ Nhiệm.</t>
+          <t>Chỉ ghi cho Chủ Nhiệm: một lớp của sheet LỚP; sheet LỚP trống thì ghi dạng khối/số thứ tự (vd 1/1) hoặc khối rồi tên lớp (vd 1D15). Mỗi lớp nhiều nhất một Chủ Nhiệm.</t>
         </is>
       </c>
     </row>
@@ -5407,7 +6364,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Dòng Chủ Nhiệm: ghi Có nếu lớp học ở cơ sở 2. Dòng khác: ghi Có nếu GV chỉ dạy ở cơ sở 2. Mỗi buổi, một GV chỉ dạy ở một cơ sở.</t>
+          <t>Dòng Chủ Nhiệm: ghi Có nếu lớp học ở cơ sở 2 (hoặc ghi ở sheet LỚP). Dòng khác: ghi Có nếu GV chỉ dạy ở cơ sở 2. Mỗi buổi, một GV chỉ dạy ở một cơ sở.</t>
         </is>
       </c>
     </row>
@@ -5443,7 +6400,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối k ghi số tiết/tuần của môn ở khối k (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn.</t>
+          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
         </is>
       </c>
     </row>
@@ -5563,7 +6520,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Khối mà Quản Lý được dạy môn này, vd Kỹ năng sống: 4.</t>
+          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
         </is>
       </c>
     </row>
@@ -5738,334 +6695,346 @@
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LUẬT</t>
+          <t>LỚP</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở 2 ghi Có nếu lớp học ở cơ sở 2. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Không xếp vào</t>
+          <t>LUẬT</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
+          <t>LUẬT: Ở đâu · Không xếp vào</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Cố định vào</t>
+          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT: Ở đâu · Cố định vào</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
+          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
+          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học trước</t>
+          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Đi cùng nhau · Học trước</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: cấu trúc của TKB</t>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="25" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I300"/>
+  <dimension ref="A1:J300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -464,6 +464,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -510,6 +511,11 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Buổi Nghỉ</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Chức Vụ Thêm</t>
         </is>
       </c>
     </row>
@@ -523,6 +529,7 @@
       <c r="G2" s="3" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="n"/>
@@ -534,6 +541,7 @@
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="n"/>
@@ -545,6 +553,7 @@
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="n"/>
@@ -556,6 +565,7 @@
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="n"/>
@@ -567,6 +577,7 @@
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="n"/>
@@ -578,6 +589,7 @@
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="n"/>
@@ -589,6 +601,7 @@
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="n"/>
@@ -600,6 +613,7 @@
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="n"/>
@@ -611,6 +625,7 @@
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="n"/>
@@ -622,6 +637,7 @@
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="5" t="n"/>
@@ -6253,7 +6269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6280,7 +6296,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên một dòng. Năm cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ không bắt buộc (để trống hoặc xóa cột).</t>
+          <t>Mỗi giáo viên một dòng. Sáu cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ, Chức Vụ Thêm không bắt buộc (để trống hoặc xóa cột).</t>
         </is>
       </c>
     </row>
@@ -6395,646 +6411,658 @@
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC</t>
+          <t>NHÂN SỰ: Chức Vụ Thêm</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
+          <t>Các chức vụ khác người này cũng giữ, cách nhau bằng dấu phẩy: Bộ Môn hoặc chức vụ GV chuyên biệt (vd Tiếng Anh). Người đó dạy được cả các môn của các chức vụ này, ở mọi lớp, trong định mức; vd Chủ Nhiệm ghi Bộ Môn thì dạy được cả các lớp khác. Chủ Nhiệm có chức vụ thêm dạy phần GVCN nhận trọn của lớp mình (không nhận thêm cho đủ định mức), phần định mức còn lại dùng cho chức vụ thêm. Mã GV theo chức vụ chính (cột Chức Vụ).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Quy ước các ô quy định</t>
+          <t>CHƯƠNG TRÌNH HỌC</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
+          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH</t>
+          <t>Quy ước các ô quy định</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
+          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
+          <t>QUY ĐỊNH</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
+          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
+          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
+          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
+          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
+          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
+          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
+          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
+          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
+          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
+          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
+          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
+          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
+          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
+          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
+          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
+          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
+          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
+          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
+          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
+          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
+          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
+          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
+          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
+          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
+          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
+          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
+          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
+          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
+          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CHỨC VỤ</t>
+          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
+          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LỚP</t>
+          <t>CHỨC VỤ</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở 2 ghi Có nếu lớp học ở cơ sở 2. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
+          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LUẬT</t>
+          <t>LỚP</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở 2 ghi Có nếu lớp học ở cơ sở 2. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Không xếp vào</t>
+          <t>LUẬT</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
+          <t>LUẬT: Ở đâu · Không xếp vào</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Cố định vào</t>
+          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT: Ở đâu · Cố định vào</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
+          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
+          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học trước</t>
+          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Đi cùng nhau · Học trước</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: cấu trúc của TKB</t>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="25" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J300"/>
+  <dimension ref="A1:K300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,7 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -516,6 +517,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Chức Vụ Thêm</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Nhãn</t>
         </is>
       </c>
     </row>
@@ -530,6 +536,7 @@
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="n"/>
@@ -542,6 +549,7 @@
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="n"/>
@@ -554,6 +562,7 @@
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="n"/>
@@ -566,6 +575,7 @@
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="n"/>
@@ -578,6 +588,7 @@
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="n"/>
@@ -590,6 +601,7 @@
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="n"/>
@@ -602,6 +614,7 @@
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="n"/>
@@ -614,6 +627,7 @@
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="n"/>
@@ -626,6 +640,7 @@
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="n"/>
@@ -638,6 +653,7 @@
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="5" t="n"/>
@@ -3134,12 +3150,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C300"/>
+  <dimension ref="A1:D300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -3158,56 +3175,71 @@
           <t>Cơ sở 2</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Nhãn</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="6" t="n"/>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="6" t="n"/>
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="6" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -6269,7 +6301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6296,7 +6328,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên một dòng. Sáu cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ, Chức Vụ Thêm không bắt buộc (để trống hoặc xóa cột).</t>
+          <t>Mỗi giáo viên một dòng. Bảy cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ, Chức Vụ Thêm, Nhãn không bắt buộc (để trống hoặc xóa cột).</t>
         </is>
       </c>
     </row>
@@ -6423,646 +6455,658 @@
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC</t>
+          <t>NHÂN SỰ: Nhãn</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
+          <t>Các nhãn tự đặt, cách nhau bằng dấu phẩy (vd Bán thời gian, Tổ Toán). Cột Giáo viên của sheet LUẬT ghi một nhãn là mọi GV có nhãn đó, vd luật Bán thời gian không dạy buổi chiều. Thai Sản, Hợp Đồng, Cơ sở 2 ghi Có cũng là nhãn cùng tên.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Quy ước các ô quy định</t>
+          <t>CHƯƠNG TRÌNH HỌC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
+          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH</t>
+          <t>Quy ước các ô quy định</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
+          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
+          <t>QUY ĐỊNH</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
+          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
+          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
+          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
+          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
+          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
+          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
+          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
+          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
+          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
+          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
+          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
+          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
+          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
+          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
+          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
+          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
+          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
+          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
+          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
+          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
+          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
+          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
+          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
+          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
+          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
+          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
+          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
+          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
+          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CHỨC VỤ</t>
+          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
+          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LỚP</t>
+          <t>CHỨC VỤ</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở 2 ghi Có nếu lớp học ở cơ sở 2. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
+          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LUẬT</t>
+          <t>LỚP</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở 2 ghi Có nếu lớp học ở cơ sở 2, cột Nhãn ghi các nhãn tự đặt cách nhau dấu phẩy (vd Song ngữ; không trùng tên lớp): cột Lớp của sheet LUẬT ghi nhãn là mọi lớp có nhãn đó, lớp ghi Có ở cột Cơ sở 2 có nhãn Cơ sở 2. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Không xếp vào</t>
+          <t>LUẬT</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
+          <t>LUẬT: Ở đâu · Không xếp vào</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Cố định vào</t>
+          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT: Ở đâu · Cố định vào</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
+          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
+          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học trước</t>
+          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Đi cùng nhau · Học trước</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: cấu trúc của TKB</t>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="25" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -3155,7 +3155,7 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Cơ sở 2</t>
+          <t>Cơ sở</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -5554,7 +5554,7 @@
       <c r="W17" s="3" t="n"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>Hạn chế để một giáo viên dạy ở cả hai cơ sở trong cùng một ngày (ưu tiên rất cao)</t>
+          <t>Hạn chế để một giáo viên đổi cơ sở trong cùng một ngày (dạy ở hai cơ sở trở lên) (ưu tiên rất cao)</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở 2 ghi Có nếu lớp học ở cơ sở 2, cột Nhãn ghi các nhãn tự đặt cách nhau dấu phẩy (vd Song ngữ; không trùng tên lớp): cột Lớp của sheet LUẬT ghi nhãn là mọi lớp có nhãn đó, lớp ghi Có ở cột Cơ sở 2 có nhãn Cơ sở 2. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
+          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở ghi tên cơ sở (điểm trường) lớp học, tùy ý, bao nhiêu cơ sở cũng được (trống: Cơ sở 1), cột Nhãn ghi các nhãn tự đặt cách nhau dấu phẩy (vd Song ngữ; không trùng tên lớp): cột Lớp của sheet LUẬT ghi nhãn hay tên cơ sở là mọi lớp có nhãn đó, ở cơ sở đó. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
         </is>
       </c>
     </row>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K300"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -466,6 +466,7 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -522,6 +523,11 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Nhãn</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Thứ Tự Bù</t>
         </is>
       </c>
     </row>
@@ -537,6 +543,7 @@
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="n"/>
@@ -550,6 +557,7 @@
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="n"/>
@@ -563,6 +571,7 @@
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="n"/>
@@ -576,6 +585,7 @@
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="n"/>
@@ -589,6 +599,7 @@
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="n"/>
@@ -602,6 +613,7 @@
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="n"/>
@@ -615,6 +627,7 @@
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="n"/>
@@ -628,6 +641,7 @@
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="n"/>
@@ -641,6 +655,7 @@
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="n"/>
@@ -654,6 +669,7 @@
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="5" t="n"/>
@@ -6301,7 +6317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6328,7 +6344,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên một dòng. Bảy cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ, Chức Vụ Thêm, Nhãn không bắt buộc (để trống hoặc xóa cột).</t>
+          <t>Mỗi giáo viên một dòng. Tám cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ, Chức Vụ Thêm, Nhãn, Thứ Tự Bù không bắt buộc (để trống hoặc xóa cột).</t>
         </is>
       </c>
     </row>
@@ -6467,646 +6483,658 @@
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC</t>
+          <t>NHÂN SỰ: Thứ Tự Bù</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
+          <t>Ai dạy bù trước khi phải bù giờ: số nguyên dương, 1 là bù trước nhất; người cùng số bù ngang nhau. Để trống: GVCN hợp đồng 1, GVCN 2, bộ môn hợp đồng 3, bộ môn 4. Chỉ có tác dụng với người được dạy bù (sheet QUY ĐỊNH, không thai sản).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Quy ước các ô quy định</t>
+          <t>CHƯƠNG TRÌNH HỌC</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
+          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH</t>
+          <t>Quy ước các ô quy định</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
+          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
+          <t>QUY ĐỊNH</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
+          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
+          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
+          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
+          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
+          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
+          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
+          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
+          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
+          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
+          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
+          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
+          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
+          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
+          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
+          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
+          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
+          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
+          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
+          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
+          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
+          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
+          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
+          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
+          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
+          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
+          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
+          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
+          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
+          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CHỨC VỤ</t>
+          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
+          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LỚP</t>
+          <t>CHỨC VỤ</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở ghi tên cơ sở (điểm trường) lớp học, tùy ý, bao nhiêu cơ sở cũng được (trống: Cơ sở 1), cột Nhãn ghi các nhãn tự đặt cách nhau dấu phẩy (vd Song ngữ; không trùng tên lớp): cột Lớp của sheet LUẬT ghi nhãn hay tên cơ sở là mọi lớp có nhãn đó, ở cơ sở đó. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
+          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LUẬT</t>
+          <t>LỚP</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở ghi tên cơ sở (điểm trường) lớp học, tùy ý, bao nhiêu cơ sở cũng được (trống: Cơ sở 1), cột Nhãn ghi các nhãn tự đặt cách nhau dấu phẩy (vd Song ngữ; không trùng tên lớp): cột Lớp của sheet LUẬT ghi nhãn hay tên cơ sở là mọi lớp có nhãn đó, ở cơ sở đó. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Không xếp vào</t>
+          <t>LUẬT</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
+          <t>LUẬT: Ở đâu · Không xếp vào</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Cố định vào</t>
+          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT: Ở đâu · Cố định vào</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
+          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
+          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học trước</t>
+          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Đi cùng nhau · Học trước</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: cấu trúc của TKB</t>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
         </is>
       </c>
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="25" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NHÂN SỰ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHƯƠNG TRÌNH HỌC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LỚP" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHỨC VỤ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUY ĐỊNH" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LUẬT" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HƯỚNG DẪN" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHÒNG" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHỨC VỤ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QUY ĐỊNH" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LUẬT" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HƯỚNG DẪN" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4135,6 +4136,991 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E300"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Phòng</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cơ sở</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Môn</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Khối</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sức chứa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="3" t="n"/>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="D12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="D13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="D14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="D15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="D16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="D17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="D19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="D20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="D21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="D22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="D23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="D24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="D25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="D26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="D27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="D28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="D29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="D30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="D31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="D32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="D33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="D35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="D36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="D37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="D38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="D39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="D40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="D41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="D42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="D43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="5" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="D54" s="5" t="n"/>
+    </row>
+    <row r="55">
+      <c r="D55" s="5" t="n"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="5" t="n"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="5" t="n"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="5" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="5" t="n"/>
+    </row>
+    <row r="61">
+      <c r="D61" s="5" t="n"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="5" t="n"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="5" t="n"/>
+    </row>
+    <row r="64">
+      <c r="D64" s="5" t="n"/>
+    </row>
+    <row r="65">
+      <c r="D65" s="5" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="5" t="n"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="5" t="n"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="5" t="n"/>
+    </row>
+    <row r="70">
+      <c r="D70" s="5" t="n"/>
+    </row>
+    <row r="71">
+      <c r="D71" s="5" t="n"/>
+    </row>
+    <row r="72">
+      <c r="D72" s="5" t="n"/>
+    </row>
+    <row r="73">
+      <c r="D73" s="5" t="n"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="5" t="n"/>
+    </row>
+    <row r="75">
+      <c r="D75" s="5" t="n"/>
+    </row>
+    <row r="76">
+      <c r="D76" s="5" t="n"/>
+    </row>
+    <row r="77">
+      <c r="D77" s="5" t="n"/>
+    </row>
+    <row r="78">
+      <c r="D78" s="5" t="n"/>
+    </row>
+    <row r="79">
+      <c r="D79" s="5" t="n"/>
+    </row>
+    <row r="80">
+      <c r="D80" s="5" t="n"/>
+    </row>
+    <row r="81">
+      <c r="D81" s="5" t="n"/>
+    </row>
+    <row r="82">
+      <c r="D82" s="5" t="n"/>
+    </row>
+    <row r="83">
+      <c r="D83" s="5" t="n"/>
+    </row>
+    <row r="84">
+      <c r="D84" s="5" t="n"/>
+    </row>
+    <row r="85">
+      <c r="D85" s="5" t="n"/>
+    </row>
+    <row r="86">
+      <c r="D86" s="5" t="n"/>
+    </row>
+    <row r="87">
+      <c r="D87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="D88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="D89" s="5" t="n"/>
+    </row>
+    <row r="90">
+      <c r="D90" s="5" t="n"/>
+    </row>
+    <row r="91">
+      <c r="D91" s="5" t="n"/>
+    </row>
+    <row r="92">
+      <c r="D92" s="5" t="n"/>
+    </row>
+    <row r="93">
+      <c r="D93" s="5" t="n"/>
+    </row>
+    <row r="94">
+      <c r="D94" s="5" t="n"/>
+    </row>
+    <row r="95">
+      <c r="D95" s="5" t="n"/>
+    </row>
+    <row r="96">
+      <c r="D96" s="5" t="n"/>
+    </row>
+    <row r="97">
+      <c r="D97" s="5" t="n"/>
+    </row>
+    <row r="98">
+      <c r="D98" s="5" t="n"/>
+    </row>
+    <row r="99">
+      <c r="D99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="D100" s="5" t="n"/>
+    </row>
+    <row r="101">
+      <c r="D101" s="5" t="n"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="5" t="n"/>
+    </row>
+    <row r="103">
+      <c r="D103" s="5" t="n"/>
+    </row>
+    <row r="104">
+      <c r="D104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="D105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="D106" s="5" t="n"/>
+    </row>
+    <row r="107">
+      <c r="D107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="D108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="D110" s="5" t="n"/>
+    </row>
+    <row r="111">
+      <c r="D111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="D112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="D113" s="5" t="n"/>
+    </row>
+    <row r="114">
+      <c r="D114" s="5" t="n"/>
+    </row>
+    <row r="115">
+      <c r="D115" s="5" t="n"/>
+    </row>
+    <row r="116">
+      <c r="D116" s="5" t="n"/>
+    </row>
+    <row r="117">
+      <c r="D117" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="D118" s="5" t="n"/>
+    </row>
+    <row r="119">
+      <c r="D119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="D120" s="5" t="n"/>
+    </row>
+    <row r="121">
+      <c r="D121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="D122" s="5" t="n"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="5" t="n"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="5" t="n"/>
+    </row>
+    <row r="125">
+      <c r="D125" s="5" t="n"/>
+    </row>
+    <row r="126">
+      <c r="D126" s="5" t="n"/>
+    </row>
+    <row r="127">
+      <c r="D127" s="5" t="n"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="5" t="n"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="5" t="n"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="5" t="n"/>
+    </row>
+    <row r="131">
+      <c r="D131" s="5" t="n"/>
+    </row>
+    <row r="132">
+      <c r="D132" s="5" t="n"/>
+    </row>
+    <row r="133">
+      <c r="D133" s="5" t="n"/>
+    </row>
+    <row r="134">
+      <c r="D134" s="5" t="n"/>
+    </row>
+    <row r="135">
+      <c r="D135" s="5" t="n"/>
+    </row>
+    <row r="136">
+      <c r="D136" s="5" t="n"/>
+    </row>
+    <row r="137">
+      <c r="D137" s="5" t="n"/>
+    </row>
+    <row r="138">
+      <c r="D138" s="5" t="n"/>
+    </row>
+    <row r="139">
+      <c r="D139" s="5" t="n"/>
+    </row>
+    <row r="140">
+      <c r="D140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="D141" s="5" t="n"/>
+    </row>
+    <row r="142">
+      <c r="D142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="D143" s="5" t="n"/>
+    </row>
+    <row r="144">
+      <c r="D144" s="5" t="n"/>
+    </row>
+    <row r="145">
+      <c r="D145" s="5" t="n"/>
+    </row>
+    <row r="146">
+      <c r="D146" s="5" t="n"/>
+    </row>
+    <row r="147">
+      <c r="D147" s="5" t="n"/>
+    </row>
+    <row r="148">
+      <c r="D148" s="5" t="n"/>
+    </row>
+    <row r="149">
+      <c r="D149" s="5" t="n"/>
+    </row>
+    <row r="150">
+      <c r="D150" s="5" t="n"/>
+    </row>
+    <row r="151">
+      <c r="D151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="D152" s="5" t="n"/>
+    </row>
+    <row r="153">
+      <c r="D153" s="5" t="n"/>
+    </row>
+    <row r="154">
+      <c r="D154" s="5" t="n"/>
+    </row>
+    <row r="155">
+      <c r="D155" s="5" t="n"/>
+    </row>
+    <row r="156">
+      <c r="D156" s="5" t="n"/>
+    </row>
+    <row r="157">
+      <c r="D157" s="5" t="n"/>
+    </row>
+    <row r="158">
+      <c r="D158" s="5" t="n"/>
+    </row>
+    <row r="159">
+      <c r="D159" s="5" t="n"/>
+    </row>
+    <row r="160">
+      <c r="D160" s="5" t="n"/>
+    </row>
+    <row r="161">
+      <c r="D161" s="5" t="n"/>
+    </row>
+    <row r="162">
+      <c r="D162" s="5" t="n"/>
+    </row>
+    <row r="163">
+      <c r="D163" s="5" t="n"/>
+    </row>
+    <row r="164">
+      <c r="D164" s="5" t="n"/>
+    </row>
+    <row r="165">
+      <c r="D165" s="5" t="n"/>
+    </row>
+    <row r="166">
+      <c r="D166" s="5" t="n"/>
+    </row>
+    <row r="167">
+      <c r="D167" s="5" t="n"/>
+    </row>
+    <row r="168">
+      <c r="D168" s="5" t="n"/>
+    </row>
+    <row r="169">
+      <c r="D169" s="5" t="n"/>
+    </row>
+    <row r="170">
+      <c r="D170" s="5" t="n"/>
+    </row>
+    <row r="171">
+      <c r="D171" s="5" t="n"/>
+    </row>
+    <row r="172">
+      <c r="D172" s="5" t="n"/>
+    </row>
+    <row r="173">
+      <c r="D173" s="5" t="n"/>
+    </row>
+    <row r="174">
+      <c r="D174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="D175" s="5" t="n"/>
+    </row>
+    <row r="176">
+      <c r="D176" s="5" t="n"/>
+    </row>
+    <row r="177">
+      <c r="D177" s="5" t="n"/>
+    </row>
+    <row r="178">
+      <c r="D178" s="5" t="n"/>
+    </row>
+    <row r="179">
+      <c r="D179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="D180" s="5" t="n"/>
+    </row>
+    <row r="181">
+      <c r="D181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="D182" s="5" t="n"/>
+    </row>
+    <row r="183">
+      <c r="D183" s="5" t="n"/>
+    </row>
+    <row r="184">
+      <c r="D184" s="5" t="n"/>
+    </row>
+    <row r="185">
+      <c r="D185" s="5" t="n"/>
+    </row>
+    <row r="186">
+      <c r="D186" s="5" t="n"/>
+    </row>
+    <row r="187">
+      <c r="D187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="D188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="D189" s="5" t="n"/>
+    </row>
+    <row r="190">
+      <c r="D190" s="5" t="n"/>
+    </row>
+    <row r="191">
+      <c r="D191" s="5" t="n"/>
+    </row>
+    <row r="192">
+      <c r="D192" s="5" t="n"/>
+    </row>
+    <row r="193">
+      <c r="D193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="D194" s="5" t="n"/>
+    </row>
+    <row r="195">
+      <c r="D195" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="D196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="D197" s="5" t="n"/>
+    </row>
+    <row r="198">
+      <c r="D198" s="5" t="n"/>
+    </row>
+    <row r="199">
+      <c r="D199" s="5" t="n"/>
+    </row>
+    <row r="200">
+      <c r="D200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="D201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="D202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="D203" s="5" t="n"/>
+    </row>
+    <row r="204">
+      <c r="D204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="D205" s="5" t="n"/>
+    </row>
+    <row r="206">
+      <c r="D206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="D207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="D208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="D209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="D210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="D211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="D212" s="5" t="n"/>
+    </row>
+    <row r="213">
+      <c r="D213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="D214" s="5" t="n"/>
+    </row>
+    <row r="215">
+      <c r="D215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="D216" s="5" t="n"/>
+    </row>
+    <row r="217">
+      <c r="D217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="D218" s="5" t="n"/>
+    </row>
+    <row r="219">
+      <c r="D219" s="5" t="n"/>
+    </row>
+    <row r="220">
+      <c r="D220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="D221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="D222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="D223" s="5" t="n"/>
+    </row>
+    <row r="224">
+      <c r="D224" s="5" t="n"/>
+    </row>
+    <row r="225">
+      <c r="D225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="D226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="D227" s="5" t="n"/>
+    </row>
+    <row r="228">
+      <c r="D228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="D229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="D230" s="5" t="n"/>
+    </row>
+    <row r="231">
+      <c r="D231" s="5" t="n"/>
+    </row>
+    <row r="232">
+      <c r="D232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="D233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="D234" s="5" t="n"/>
+    </row>
+    <row r="235">
+      <c r="D235" s="5" t="n"/>
+    </row>
+    <row r="236">
+      <c r="D236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="D237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="D238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="D239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="D240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="D241" s="5" t="n"/>
+    </row>
+    <row r="242">
+      <c r="D242" s="5" t="n"/>
+    </row>
+    <row r="243">
+      <c r="D243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="D244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="D245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="D246" s="5" t="n"/>
+    </row>
+    <row r="247">
+      <c r="D247" s="5" t="n"/>
+    </row>
+    <row r="248">
+      <c r="D248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="D249" s="5" t="n"/>
+    </row>
+    <row r="250">
+      <c r="D250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="D251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="D252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="D253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="D254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="D255" s="5" t="n"/>
+    </row>
+    <row r="256">
+      <c r="D256" s="5" t="n"/>
+    </row>
+    <row r="257">
+      <c r="D257" s="5" t="n"/>
+    </row>
+    <row r="258">
+      <c r="D258" s="5" t="n"/>
+    </row>
+    <row r="259">
+      <c r="D259" s="5" t="n"/>
+    </row>
+    <row r="260">
+      <c r="D260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="D261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="D262" s="5" t="n"/>
+    </row>
+    <row r="263">
+      <c r="D263" s="5" t="n"/>
+    </row>
+    <row r="264">
+      <c r="D264" s="5" t="n"/>
+    </row>
+    <row r="265">
+      <c r="D265" s="5" t="n"/>
+    </row>
+    <row r="266">
+      <c r="D266" s="5" t="n"/>
+    </row>
+    <row r="267">
+      <c r="D267" s="5" t="n"/>
+    </row>
+    <row r="268">
+      <c r="D268" s="5" t="n"/>
+    </row>
+    <row r="269">
+      <c r="D269" s="5" t="n"/>
+    </row>
+    <row r="270">
+      <c r="D270" s="5" t="n"/>
+    </row>
+    <row r="271">
+      <c r="D271" s="5" t="n"/>
+    </row>
+    <row r="272">
+      <c r="D272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="D273" s="5" t="n"/>
+    </row>
+    <row r="274">
+      <c r="D274" s="5" t="n"/>
+    </row>
+    <row r="275">
+      <c r="D275" s="5" t="n"/>
+    </row>
+    <row r="276">
+      <c r="D276" s="5" t="n"/>
+    </row>
+    <row r="277">
+      <c r="D277" s="5" t="n"/>
+    </row>
+    <row r="278">
+      <c r="D278" s="5" t="n"/>
+    </row>
+    <row r="279">
+      <c r="D279" s="5" t="n"/>
+    </row>
+    <row r="280">
+      <c r="D280" s="5" t="n"/>
+    </row>
+    <row r="281">
+      <c r="D281" s="5" t="n"/>
+    </row>
+    <row r="282">
+      <c r="D282" s="5" t="n"/>
+    </row>
+    <row r="283">
+      <c r="D283" s="5" t="n"/>
+    </row>
+    <row r="284">
+      <c r="D284" s="5" t="n"/>
+    </row>
+    <row r="285">
+      <c r="D285" s="5" t="n"/>
+    </row>
+    <row r="286">
+      <c r="D286" s="5" t="n"/>
+    </row>
+    <row r="287">
+      <c r="D287" s="5" t="n"/>
+    </row>
+    <row r="288">
+      <c r="D288" s="5" t="n"/>
+    </row>
+    <row r="289">
+      <c r="D289" s="5" t="n"/>
+    </row>
+    <row r="290">
+      <c r="D290" s="5" t="n"/>
+    </row>
+    <row r="291">
+      <c r="D291" s="5" t="n"/>
+    </row>
+    <row r="292">
+      <c r="D292" s="5" t="n"/>
+    </row>
+    <row r="293">
+      <c r="D293" s="5" t="n"/>
+    </row>
+    <row r="294">
+      <c r="D294" s="5" t="n"/>
+    </row>
+    <row r="295">
+      <c r="D295" s="5" t="n"/>
+    </row>
+    <row r="296">
+      <c r="D296" s="5" t="n"/>
+    </row>
+    <row r="297">
+      <c r="D297" s="5" t="n"/>
+    </row>
+    <row r="298">
+      <c r="D298" s="5" t="n"/>
+    </row>
+    <row r="299">
+      <c r="D299" s="5" t="n"/>
+    </row>
+    <row r="300">
+      <c r="D300" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4199,7 +5185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4502,7 +5488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6311,13 +7297,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6807,334 +7793,346 @@
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LUẬT</t>
+          <t>PHÒNG</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Không bắt buộc. Mỗi dòng một phòng học dùng chung (phòng Tin, phòng đa năng, sân trường): cột Phòng ghi tên phòng, cột Cơ sở ghi tên cơ sở như cột Cơ sở của sheet LỚP (trống: Cơ sở 1), cột Môn ghi các môn học ở phòng này cách nhau dấu phẩy (đúng tên trong sheet CHƯƠNG TRÌNH HỌC, hoặc một nhãn môn là tiêu đề một cột Có/Không của sheet đó), cột Khối ghi các khối dùng phòng (trống: mọi khối), cột Sức chứa ghi số lớp học cùng lúc trong phòng (trống: 1; vd sân trường 3). Luật cứng: tiết của môn, khối, cơ sở có phòng ghi ở đây phải học ở một phòng như vậy, mỗi giờ học không quá sức chứa; tên phòng ghi trong TKB và file TKB phòng. Môn không có phòng nào ghi thì học ở lớp.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Không xếp vào</t>
+          <t>LUẬT</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
+          <t>LUẬT: Ở đâu · Không xếp vào</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Cố định vào</t>
+          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT: Ở đâu · Cố định vào</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
+          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
+          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học trước</t>
+          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Đi cùng nhau · Học trước</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: cấu trúc của TKB</t>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
         </is>
       </c>
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="25" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -7303,7 +7303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7925,214 +7925,238 @@
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Đi cùng nhau · Học cùng giờ</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học Môn và các môn ở cột Môn thứ hai cùng giờ, cùng số tiết mỗi tuần, mỗi môn một người dạy, lớp tính một tiết ở giờ đó. Dùng cho lớp chia nhóm, vd nửa lớp học Tin học, nửa lớp học Tiếng Anh; hoặc giáo viên dạy kèm: ghi môn riêng Trợ giảng Tiếng Anh (cùng số tiết, chức vụ Trợ Giảng dạy) học cùng giờ với Tiếng Anh. Chỉ ghi Bắt buộc = Có.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Cùng giờ</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+          <t>Các tiết của Môn và của Môn thứ hai luôn học cùng giờ, cùng số tiết mỗi tuần: lớp chia nhóm (mỗi nhóm học một môn, mỗi môn một người dạy) hoặc giáo viên chính và trợ giảng (ghi trợ giảng thành một môn riêng, vd Trợ giảng Tiếng Anh). Với mỗi là Lớp, chỉ ghi Bắt buộc; lớp tính một tiết ở giờ đó.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: cấu trúc của TKB</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="69" ht="25" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="25" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="25" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -7303,7 +7303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7937,226 +7937,238 @@
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Đi cùng nhau · Ghép lớp</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Các lớp ghi ở cột Lớp (hoặc các lớp của khối ở cột Khối) học chung Môn: cùng giờ, cùng số tiết mỗi tuần, một người dạy cả nhóm, người đó tính một tiết ở giờ đó, vd Thể dục lớp 3/1, 3/2 học chung một sân. Ghi Môn thứ hai thì lớp có môn đó học chung với các lớp có Môn (mỗi lớp một môn), vd lớp ghép hai khối. Muốn ghép riêng từng khối: dùng Tự ghép, Với mỗi Khối. Chỉ ghi Bắt buộc = Có.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Cùng giờ</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn và của Môn thứ hai luôn học cùng giờ, cùng số tiết mỗi tuần: lớp chia nhóm (mỗi nhóm học một môn, mỗi môn một người dạy) hoặc giáo viên chính và trợ giảng (ghi trợ giảng thành một môn riêng, vd Trợ giảng Tiếng Anh). Với mỗi là Lớp, chỉ ghi Bắt buộc; lớp tính một tiết ở giờ đó.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Cùng giờ</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Các tiết luôn học cùng giờ, cùng số tiết mỗi tuần; chỉ ghi Bắt buộc. Mỗi môn một người (để trống So sánh): mỗi lớp học Môn và Môn thứ hai cùng giờ, lớp tính một tiết ở giờ đó: lớp chia nhóm (mỗi nhóm học một môn, mỗi môn một người dạy) hoặc giáo viên chính và trợ giảng (ghi trợ giảng thành một môn riêng, vd Trợ giảng Tiếng Anh); Với mỗi là Lớp. Cùng một người: ghép lớp, các lớp (của cả trường, hoặc mỗi khối, mỗi cơ sở ở cột Với mỗi) học Môn (và Môn thứ hai nếu ghi) cùng giờ, một người dạy, người đó tính một tiết ở giờ đó. So sánh: Mỗi môn một người, Cùng một người.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="25" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="70" ht="25" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: cấu trúc của TKB</t>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
         </is>
       </c>
     </row>
     <row r="71" ht="25" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="25" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -7303,7 +7303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7325,850 +7325,898 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ</t>
+          <t>BẮT ĐẦU NHANH</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên một dòng. Tám cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ, Chức Vụ Thêm, Nhãn, Thứ Tự Bù không bắt buộc (để trống hoặc xóa cột).</t>
+          <t>Chỉ cần điền hai sheet: NHÂN SỰ (bốn cột đầu: Họ và Tên, Chức Vụ, Lớp, Số Tiết/Tuần) và CHƯƠNG TRÌNH HỌC (số tiết/tuần của từng môn ở các cột Khối). Các sheet, các cột khác đã có sẵn giá trị mặc định: để nguyên nếu trường không cần.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Họ và Tên</t>
+          <t>BẮT ĐẦU NHANH: Chức Vụ</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Tên giáo viên; người chưa tuyển được ghi "chưa có".</t>
+          <t>Chủ Nhiệm (ghi lớp ở cột Lớp, vd 1/1), Bộ Môn, Quản Lý, hoặc tên môn GV chuyên dạy (vd Tiếng Anh). Không ghi số thứ tự.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Chức Vụ</t>
+          <t>BẮT ĐẦU NHANH: lưu ý</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Chủ Nhiệm, Bộ Môn, Quản Lý, một chức vụ của sheet CHỨC VỤ hoặc tên một môn trong sheet CHƯƠNG TRÌNH HỌC (GV chuyên biệt). Không ghi số thứ tự: chương trình tự đánh số theo thứ tự dòng.</t>
+          <t>Giữ nguyên tên sheet và tên cột. Người đã nghỉ thì xóa hẳn dòng (dòng ẩn vẫn được tính). Ô Có/Không ghi Có hoặc để trống. Lưu file dạng Excel .xlsx.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Lớp</t>
+          <t>BẮT ĐẦU NHANH: không cần Excel</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chỉ ghi cho Chủ Nhiệm: một lớp của sheet LỚP; sheet LỚP trống thì ghi dạng khối/số thứ tự (vd 1/1) hoặc khối rồi tên lớp (vd 1D15). Mỗi lớp nhiều nhất một Chủ Nhiệm.</t>
+          <t>Mở trang nhập liệu (TKB.exe hoặc giao_dien.py), chọn Soạn mới, rồi dán danh sách giáo viên chép từ Excel (nút Dán từ Excel… ở bước Giáo viên).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Số Tiết/Tuần</t>
+          <t>NHÂN SỰ</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Số tiết tối đa mỗi tuần (số nguyên).</t>
+          <t>Mỗi giáo viên một dòng. Tám cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ, Chức Vụ Thêm, Nhãn, Thứ Tự Bù không bắt buộc (để trống hoặc xóa cột).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Thai Sản</t>
+          <t>NHÂN SỰ: Họ và Tên</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ghi Có nếu đang hưởng chế độ thai sản: không dạy bù, chỉ dạy các lớp ở cơ sở 2.</t>
+          <t>Tên giáo viên; người chưa tuyển được ghi "chưa có".</t>
         </is>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Hợp Đồng</t>
+          <t>NHÂN SỰ: Chức Vụ</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ghi Có nếu là GV hợp đồng: khi phải bù, GVCN hợp đồng bù trước GVCN khác, bộ môn hợp đồng bù trước bộ môn khác.</t>
+          <t>Chủ Nhiệm, Bộ Môn, Quản Lý, một chức vụ của sheet CHỨC VỤ hoặc tên một môn trong sheet CHƯƠNG TRÌNH HỌC (GV chuyên biệt). Không ghi số thứ tự: chương trình tự đánh số theo thứ tự dòng.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Cơ sở 2</t>
+          <t>NHÂN SỰ: Lớp</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Dòng Chủ Nhiệm: ghi Có nếu lớp học ở cơ sở 2 (hoặc ghi ở sheet LỚP). Dòng khác: ghi Có nếu GV chỉ dạy ở cơ sở 2. Mỗi buổi, một GV chỉ dạy ở một cơ sở.</t>
+          <t>Chỉ ghi cho Chủ Nhiệm: một lớp của sheet LỚP; sheet LỚP trống thì ghi dạng khối/số thứ tự (vd 1/1) hoặc khối rồi tên lớp (vd 1D15). Mỗi lớp nhiều nhất một Chủ Nhiệm.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Lớp Đang Dạy</t>
+          <t>NHÂN SỰ: Số Tiết/Tuần</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GV bộ môn, chuyên biệt: các lớp đang dạy trong TKB cũ, cách nhau bằng dấu phẩy (vd 3D17, 3D18). TKB mới ưu tiên giữ khối, rồi giữ lớp.</t>
+          <t>Số tiết tối đa mỗi tuần (số nguyên).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Buổi Nghỉ</t>
+          <t>NHÂN SỰ: Thai Sản</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Buổi không xếp tiết: buổi cố định (vd Chiều T5, Sáng T6) hoặc số buổi bất kỳ (vd 2 buổi chiều), cách nhau bằng dấu phẩy. GVCN không nghỉ được buổi có tiết Luôn do GVCN dạy (sheet QUY ĐỊNH).</t>
+          <t>Ghi Có nếu đang hưởng chế độ thai sản: không dạy bù, chỉ dạy các lớp ở cơ sở 2.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Chức Vụ Thêm</t>
+          <t>NHÂN SỰ: Hợp Đồng</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Các chức vụ khác người này cũng giữ, cách nhau bằng dấu phẩy: Bộ Môn hoặc chức vụ GV chuyên biệt (vd Tiếng Anh). Người đó dạy được cả các môn của các chức vụ này, ở mọi lớp, trong định mức; vd Chủ Nhiệm ghi Bộ Môn thì dạy được cả các lớp khác. Chủ Nhiệm có chức vụ thêm dạy phần GVCN nhận trọn của lớp mình (không nhận thêm cho đủ định mức), phần định mức còn lại dùng cho chức vụ thêm. Mã GV theo chức vụ chính (cột Chức Vụ).</t>
+          <t>Ghi Có nếu là GV hợp đồng: khi phải bù, GVCN hợp đồng bù trước GVCN khác, bộ môn hợp đồng bù trước bộ môn khác.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Nhãn</t>
+          <t>NHÂN SỰ: Cơ sở 2</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Các nhãn tự đặt, cách nhau bằng dấu phẩy (vd Bán thời gian, Tổ Toán). Cột Giáo viên của sheet LUẬT ghi một nhãn là mọi GV có nhãn đó, vd luật Bán thời gian không dạy buổi chiều. Thai Sản, Hợp Đồng, Cơ sở 2 ghi Có cũng là nhãn cùng tên.</t>
+          <t>Dòng Chủ Nhiệm: ghi Có nếu lớp học ở cơ sở 2 (hoặc ghi ở sheet LỚP). Dòng khác: ghi Có nếu GV chỉ dạy ở cơ sở 2. Mỗi buổi, một GV chỉ dạy ở một cơ sở.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>NHÂN SỰ: Thứ Tự Bù</t>
+          <t>NHÂN SỰ: Lớp Đang Dạy</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Ai dạy bù trước khi phải bù giờ: số nguyên dương, 1 là bù trước nhất; người cùng số bù ngang nhau. Để trống: GVCN hợp đồng 1, GVCN 2, bộ môn hợp đồng 3, bộ môn 4. Chỉ có tác dụng với người được dạy bù (sheet QUY ĐỊNH, không thai sản).</t>
+          <t>GV bộ môn, chuyên biệt: các lớp đang dạy trong TKB cũ, cách nhau bằng dấu phẩy (vd 3D17, 3D18). TKB mới ưu tiên giữ khối, rồi giữ lớp.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC</t>
+          <t>NHÂN SỰ: Buổi Nghỉ</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
+          <t>Buổi không xếp tiết: buổi cố định (vd Chiều T5, Sáng T6) hoặc số buổi bất kỳ (vd 2 buổi chiều), cách nhau bằng dấu phẩy. GVCN không nghỉ được buổi có tiết Luôn do GVCN dạy (sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Quy ước các ô quy định</t>
+          <t>NHÂN SỰ: Chức Vụ Thêm</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
+          <t>Các chức vụ khác người này cũng giữ, cách nhau bằng dấu phẩy: Bộ Môn hoặc chức vụ GV chuyên biệt (vd Tiếng Anh). Người đó dạy được cả các môn của các chức vụ này, ở mọi lớp, trong định mức; vd Chủ Nhiệm ghi Bộ Môn thì dạy được cả các lớp khác. Chủ Nhiệm có chức vụ thêm dạy phần GVCN nhận trọn của lớp mình (không nhận thêm cho đủ định mức), phần định mức còn lại dùng cho chức vụ thêm. Mã GV theo chức vụ chính (cột Chức Vụ).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH</t>
+          <t>NHÂN SỰ: Nhãn</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
+          <t>Các nhãn tự đặt, cách nhau bằng dấu phẩy (vd Bán thời gian, Tổ Toán). Cột Giáo viên của sheet LUẬT ghi một nhãn là mọi GV có nhãn đó, vd luật Bán thời gian không dạy buổi chiều. Thai Sản, Hợp Đồng, Cơ sở 2 ghi Có cũng là nhãn cùng tên.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
+          <t>NHÂN SỰ: Thứ Tự Bù</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
+          <t>Ai dạy bù trước khi phải bù giờ: số nguyên dương, 1 là bù trước nhất; người cùng số bù ngang nhau. Để trống: GVCN hợp đồng 1, GVCN 2, bộ môn hợp đồng 3, bộ môn 4. Chỉ có tác dụng với người được dạy bù (sheet QUY ĐỊNH, không thai sản).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
+          <t>CHƯƠNG TRÌNH HỌC</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
+          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
+          <t>Quy ước các ô quy định</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
+          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
+          <t>QUY ĐỊNH</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
+          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
+          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
+          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
+          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
+          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
+          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
+          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
+          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
+          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
+          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
+          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
+          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
+          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
+          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
+          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
+          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
+          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
+          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
+          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
+          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
+          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
+          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
+          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
+          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>CHỨC VỤ</t>
+          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
+          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LỚP</t>
+          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở ghi tên cơ sở (điểm trường) lớp học, tùy ý, bao nhiêu cơ sở cũng được (trống: Cơ sở 1), cột Nhãn ghi các nhãn tự đặt cách nhau dấu phẩy (vd Song ngữ; không trùng tên lớp): cột Lớp của sheet LUẬT ghi nhãn hay tên cơ sở là mọi lớp có nhãn đó, ở cơ sở đó. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
+          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>PHÒNG</t>
+          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một phòng học dùng chung (phòng Tin, phòng đa năng, sân trường): cột Phòng ghi tên phòng, cột Cơ sở ghi tên cơ sở như cột Cơ sở của sheet LỚP (trống: Cơ sở 1), cột Môn ghi các môn học ở phòng này cách nhau dấu phẩy (đúng tên trong sheet CHƯƠNG TRÌNH HỌC, hoặc một nhãn môn là tiêu đề một cột Có/Không của sheet đó), cột Khối ghi các khối dùng phòng (trống: mọi khối), cột Sức chứa ghi số lớp học cùng lúc trong phòng (trống: 1; vd sân trường 3). Luật cứng: tiết của môn, khối, cơ sở có phòng ghi ở đây phải học ở một phòng như vậy, mỗi giờ học không quá sức chứa; tên phòng ghi trong TKB và file TKB phòng. Môn không có phòng nào ghi thì học ở lớp.</t>
+          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LUẬT</t>
+          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Không xếp vào</t>
+          <t>CHỨC VỤ</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
+          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
+          <t>LỚP</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
+          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở ghi tên cơ sở (điểm trường) lớp học, tùy ý, bao nhiêu cơ sở cũng được (trống: Cơ sở 1), cột Nhãn ghi các nhãn tự đặt cách nhau dấu phẩy (vd Song ngữ; không trùng tên lớp): cột Lớp của sheet LUẬT ghi nhãn hay tên cơ sở là mọi lớp có nhãn đó, ở cơ sở đó. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Cố định vào</t>
+          <t>PHÒNG</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
+          <t>Không bắt buộc. Mỗi dòng một phòng học dùng chung (phòng Tin, phòng đa năng, sân trường): cột Phòng ghi tên phòng, cột Cơ sở ghi tên cơ sở như cột Cơ sở của sheet LỚP (trống: Cơ sở 1), cột Môn ghi các môn học ở phòng này cách nhau dấu phẩy (đúng tên trong sheet CHƯƠNG TRÌNH HỌC, hoặc một nhãn môn là tiêu đề một cột Có/Không của sheet đó), cột Khối ghi các khối dùng phòng (trống: mọi khối), cột Sức chứa ghi số lớp học cùng lúc trong phòng (trống: 1; vd sân trường 3). Luật cứng: tiết của môn, khối, cơ sở có phòng ghi ở đây phải học ở một phòng như vậy, mỗi giờ học không quá sức chứa; tên phòng ghi trong TKB và file TKB phòng. Môn không có phòng nào ghi thì học ở lớp.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Ở đâu · Không xếp vào</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
+          <t>LUẬT: Ở đâu · Cố định vào</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học trước</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học cùng giờ</t>
+          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học Môn và các môn ở cột Môn thứ hai cùng giờ, cùng số tiết mỗi tuần, mỗi môn một người dạy, lớp tính một tiết ở giờ đó. Dùng cho lớp chia nhóm, vd nửa lớp học Tin học, nửa lớp học Tiếng Anh; hoặc giáo viên dạy kèm: ghi môn riêng Trợ giảng Tiếng Anh (cùng số tiết, chức vụ Trợ Giảng dạy) học cùng giờ với Tiếng Anh. Chỉ ghi Bắt buộc = Có.</t>
+          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Ghép lớp</t>
+          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Các lớp ghi ở cột Lớp (hoặc các lớp của khối ở cột Khối) học chung Môn: cùng giờ, cùng số tiết mỗi tuần, một người dạy cả nhóm, người đó tính một tiết ở giờ đó, vd Thể dục lớp 3/1, 3/2 học chung một sân. Ghi Môn thứ hai thì lớp có môn đó học chung với các lớp có Môn (mỗi lớp một môn), vd lớp ghép hai khối. Muốn ghép riêng từng khối: dùng Tự ghép, Với mỗi Khối. Chỉ ghi Bắt buộc = Có.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Đi cùng nhau · Học trước</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Đi cùng nhau · Học cùng giờ</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học Môn và các môn ở cột Môn thứ hai cùng giờ, cùng số tiết mỗi tuần, mỗi môn một người dạy, lớp tính một tiết ở giờ đó. Dùng cho lớp chia nhóm, vd nửa lớp học Tin học, nửa lớp học Tiếng Anh; hoặc giáo viên dạy kèm: ghi môn riêng Trợ giảng Tiếng Anh (cùng số tiết, chức vụ Trợ Giảng dạy) học cùng giờ với Tiếng Anh. Chỉ ghi Bắt buộc = Có.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Đi cùng nhau · Ghép lớp</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Các lớp ghi ở cột Lớp (hoặc các lớp của khối ở cột Khối) học chung Môn: cùng giờ, cùng số tiết mỗi tuần, một người dạy cả nhóm, người đó tính một tiết ở giờ đó, vd Thể dục lớp 3/1, 3/2 học chung một sân. Ghi Môn thứ hai thì lớp có môn đó học chung với các lớp có Môn (mỗi lớp một môn), vd lớp ghép hai khối. Muốn ghép riêng từng khối: dùng Tự ghép, Với mỗi Khối. Chỉ ghi Bắt buộc = Có.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Cùng giờ</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Các tiết luôn học cùng giờ, cùng số tiết mỗi tuần; chỉ ghi Bắt buộc. Mỗi môn một người (để trống So sánh): mỗi lớp học Môn và Môn thứ hai cùng giờ, lớp tính một tiết ở giờ đó: lớp chia nhóm (mỗi nhóm học một môn, mỗi môn một người dạy) hoặc giáo viên chính và trợ giảng (ghi trợ giảng thành một môn riêng, vd Trợ giảng Tiếng Anh); Với mỗi là Lớp. Cùng một người: ghép lớp, các lớp (của cả trường, hoặc mỗi khối, mỗi cơ sở ở cột Với mỗi) học Môn (và Môn thứ hai nếu ghi) cùng giờ, một người dạy, người đó tính một tiết ở giờ đó. So sánh: Mỗi môn một người, Cùng một người.</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="69" ht="25" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="25" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="25" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: cấu trúc của TKB</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Cùng giờ</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Các tiết luôn học cùng giờ, cùng số tiết mỗi tuần; chỉ ghi Bắt buộc. Mỗi môn một người (để trống So sánh): mỗi lớp học Môn và Môn thứ hai cùng giờ, lớp tính một tiết ở giờ đó: lớp chia nhóm (mỗi nhóm học một môn, mỗi môn một người dạy) hoặc giáo viên chính và trợ giảng (ghi trợ giảng thành một môn riêng, vd Trợ giảng Tiếng Anh); Với mỗi là Lớp. Cùng một người: ghép lớp, các lớp (của cả trường, hoặc mỗi khối, mỗi cơ sở ở cột Với mỗi) học Môn (và Môn thứ hai nếu ghi) cùng giờ, một người dạy, người đó tính một tiết ở giờ đó. So sánh: Mỗi môn một người, Cùng một người.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="25" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="25" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT: Tự ghép, cột Số</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="25" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="25" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="25" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L300"/>
+  <dimension ref="A1:M300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -468,6 +468,7 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -529,6 +530,11 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Thứ Tự Bù</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Tên Viết Tắt</t>
         </is>
       </c>
     </row>
@@ -545,6 +551,7 @@
       <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="n"/>
@@ -559,6 +566,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="n"/>
@@ -573,6 +581,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="n"/>
@@ -587,6 +596,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="n"/>
@@ -601,6 +611,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="n"/>
@@ -615,6 +626,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="n"/>
@@ -629,6 +641,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="n"/>
@@ -643,6 +656,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="n"/>
@@ -657,6 +671,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="n"/>
@@ -671,6 +686,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="C12" s="5" t="n"/>
@@ -7303,7 +7319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7378,7 +7394,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên một dòng. Tám cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ, Chức Vụ Thêm, Nhãn, Thứ Tự Bù không bắt buộc (để trống hoặc xóa cột).</t>
+          <t>Mỗi giáo viên một dòng. Chín cột Thai Sản, Hợp Đồng, Cơ sở 2, Lớp Đang Dạy, Buổi Nghỉ, Chức Vụ Thêm, Nhãn, Thứ Tự Bù, Tên Viết Tắt không bắt buộc (để trống hoặc xóa cột).</t>
         </is>
       </c>
     </row>
@@ -7529,694 +7545,706 @@
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC</t>
+          <t>NHÂN SỰ: Tên Viết Tắt</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
+          <t>Tên ghi trong file TKB toàn trường (vd B.Huyền, Võ Ly). Để trống: chương trình tự viết tắt từ họ tên (tên, người trùng tên thì thêm chữ đầu của từ đứng trước, vd T.Huyền).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Quy ước các ô quy định</t>
+          <t>CHƯƠNG TRÌNH HỌC</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
+          <t>Mỗi môn một dòng: cột Môn học ghi tên môn (dùng đúng tên này ở sheet CHỨC VỤ, hoặc ở cột Chức Vụ của GV chuyên biệt chỉ dạy môn này), cột Khối &lt;tên&gt; ghi số tiết/tuần của môn ở khối đó (0 hoặc để trống: khối đó không học), các cột sau là quy định của môn. Tên khối tùy ý, vd Khối 1, Khối Lá; thêm khối thì thêm cột.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH</t>
+          <t>Quy ước các ô quy định</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
+          <t>Mỗi quy định là một cột (bảng Quy định chung: một dòng). Mỗi ô chỉ ghi Có, Không hoặc một số nguyên dương; ô trống là Không. Riêng cột Tên trong TKB ghi chữ. Xóa một cột (một dòng của bảng chung, một bảng, hoặc cả sheet QUY ĐỊNH) thì quy định đó dùng giá trị mặc định của chương trình.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
+          <t>QUY ĐỊNH</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
+          <t>Ba bảng cách nhau một dòng trống: Quy định | Giá trị; Ngày (mỗi dòng một ngày học, mỗi cột Buổi &lt;tên&gt; ghi số tiết của buổi đó); Tiết (đánh số liên tục trong ngày: sáng 4 tiết thì chiều từ tiết 5; ngày dài nhất có bao nhiêu tiết thì bấy nhiêu dòng).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
+          <t>CHƯƠNG TRÌNH HỌC: Tên trong TKB</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
+          <t>Chữ ghi trong ô TKB (cột duy nhất ghi chữ); trống: ghi đúng tên môn.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn HĐTN</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
+          <t>Có ở một môn: môn chào cờ, sinh hoạt lớp, có tiết cố định ở bảng ngày của sheet QUY ĐỊNH.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận trọn</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
+          <t>GVCN nhận hết các môn này của lớp mình; luật cứng: môn nào phải chia cho người khác thì tiết đầu tiên trong tuần do GVCN dạy.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN cắt bớt</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
+          <t>Số thứ tự 1, 2...: môn cắt trước khi các môn nhận trọn vượt định mức GVCN; mỗi môn GVCN giữ ít nhất 1 tiết.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN nhận thêm</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
+          <t>Số thứ tự 1, 2...: môn GVCN nhận thêm trước cho đủ định mức (không nhận môn của GV chuyên biệt).</t>
         </is>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
+          <t>CHƯƠNG TRÌNH HỌC: Chỉ GVCN dạy</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
+          <t>Luật cứng: chỉ GVCN của lớp được dạy.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
+          <t>CHƯƠNG TRÌNH HỌC: Bộ Môn không dạy</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
+          <t>GV bộ môn không dạy môn này; trường chưa có GV chuyên biệt của môn thì chương trình tuyển thêm. Ghi theo ngoại lệ để môn mới (ô trống) mặc nhiên bộ môn dạy được.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
+          <t>CHƯƠNG TRÌNH HỌC: Quản lý dạy khối</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
+          <t>Khối mà Quản Lý được dạy môn này (tên khối như ở cột Khối &lt;tên&gt;), vd Kỹ năng sống: 4.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
+          <t>CHƯƠNG TRÌNH HỌC: GVCN bù môn chuyên biệt</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
+          <t>Môn có GV chuyên biệt mà GVCN vẫn được dạy bù ở lớp mình (nhận sau cùng).</t>
         </is>
       </c>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
+          <t>CHƯƠNG TRÌNH HỌC: Nhóm môn</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
+          <t>Môn chính và các môn tăng cường của nó ghi cùng một số, vd Tiếng Việt và Tiếng Việt tăng cường: 1.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn tăng cường</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
+          <t>Có ở môn tăng cường của nhóm; luật cứng: tiết tăng cường đứng sau mọi tiết môn chính trong ngày và ngày đó phải có tiết môn chính; cả nhóm tính chung cho giới hạn mỗi buổi và ghép cặp.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Không ghép cặp</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
+          <t>Nhóm môn (ghi ở môn chính) không xếp thành cặp 2 tiết liền. Ghi theo ngoại lệ như cột Bộ Môn không dạy.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
+          <t>CHƯƠNG TRÌNH HỌC: Môn nặng</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
+          <t>Mục tiêu mềm: hạn chế xếp vào các tiết Hạn chế môn nặng (sheet QUY ĐỊNH).</t>
         </is>
       </c>
     </row>
     <row r="36" ht="25" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
+          <t>CHƯƠNG TRÌNH HỌC: Ưu tiên buổi sáng</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
+          <t>Mục tiêu mềm: mỗi tiết ở buổi chiều bị trừ điểm, và môn được rải đều hơn trong tuần.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="25" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
+          <t>QUY ĐỊNH: Chủ Nhiệm được dạy bù</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
+          <t>GVCN chỉ bù ở lớp mình và bù trước bộ môn.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
+          <t>QUY ĐỊNH: Bộ Môn được dạy bù</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
+          <t>Bộ môn bù khi GVCN đã bù hết mức.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
+          <t>QUY ĐỊNH: Ngày, Buổi &lt;tên buổi&gt;</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
+          <t>Bảng Ngày: mỗi dòng một ngày học, tên tùy ý (vd Thứ 2, Thứ 7, Chủ nhật), theo thứ tự trong tuần. Mỗi cột Buổi &lt;tên buổi&gt; (vd Buổi Sáng, Buổi Chiều, Buổi Tối) ghi số tiết của buổi đó trong ngày; ô trống là ngày đó không học buổi đó. Mỗi ngày một số tiết riêng được (vd chiều Thứ 5 có 4 tiết). Thêm buổi thì thêm cột, thêm ngày học thì thêm dòng; ngày không có tiết nào không phải ngày học. Tiết đánh số liên tục trong ngày theo thứ tự các cột buổi: sáng 4 tiết thì chiều bắt đầu từ tiết 5.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
+          <t>QUY ĐỊNH: Tiết HĐTN cố định</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
+          <t>Luật cứng: tiết môn HĐTN cố định của ngày đó ở mọi lớp, vd Thứ 2: 1, Thứ 6: 4.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
+          <t>QUY ĐỊNH: Xếp tiết HĐTN còn lại</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
+          <t>Luật cứng: các tiết HĐTN còn lại chỉ xếp vào các ngày này (mục tiêu mềm: gần cuối buổi).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
+          <t>QUY ĐỊNH: Luôn do GVCN dạy</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
+          <t>Luật cứng: tiết này ở mọi ngày do GVCN của lớp dạy.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>CHỨC VỤ</t>
+          <t>QUY ĐỊNH: Hạn chế môn nặng</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
+          <t>Mục tiêu mềm: mỗi tiết môn nặng ở tiết này bị trừ điểm.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LỚP</t>
+          <t>CHỨC VỤ</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở ghi tên cơ sở (điểm trường) lớp học, tùy ý, bao nhiêu cơ sở cũng được (trống: Cơ sở 1), cột Nhãn ghi các nhãn tự đặt cách nhau dấu phẩy (vd Song ngữ; không trùng tên lớp): cột Lớp của sheet LUẬT ghi nhãn hay tên cơ sở là mọi lớp có nhãn đó, ở cơ sở đó. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
+          <t>Không bắt buộc. Mỗi dòng một chức vụ GV chuyên biệt nhà trường tự đặt: cột Chức vụ ghi tên (không ghi số, không trùng Chủ Nhiệm, Bộ Môn, Quản Lý), cột Môn được dạy ghi các môn chức vụ đó dạy, cách nhau bằng dấu phẩy, đúng tên trong sheet CHƯƠNG TRÌNH HỌC, vd GV Nghệ thuật: Âm nhạc, Mỹ thuật. Ở sheet NHÂN SỰ, GV có Chức Vụ là tên đó chỉ dạy các môn này. Chức vụ không ghi ở đây mà trùng tên một môn (vd Tiếng Anh) thì chỉ dạy môn đó. Môn Bộ Môn không dạy mà chưa có GV nào dạy được thì chương trình tuyển thêm chức vụ đầu tiên ở đây dạy môn đó (không có thì chức vụ trùng tên môn).</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>PHÒNG</t>
+          <t>LỚP</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Không bắt buộc. Mỗi dòng một phòng học dùng chung (phòng Tin, phòng đa năng, sân trường): cột Phòng ghi tên phòng, cột Cơ sở ghi tên cơ sở như cột Cơ sở của sheet LỚP (trống: Cơ sở 1), cột Môn ghi các môn học ở phòng này cách nhau dấu phẩy (đúng tên trong sheet CHƯƠNG TRÌNH HỌC, hoặc một nhãn môn là tiêu đề một cột Có/Không của sheet đó), cột Khối ghi các khối dùng phòng (trống: mọi khối), cột Sức chứa ghi số lớp học cùng lúc trong phòng (trống: 1; vd sân trường 3). Luật cứng: tiết của môn, khối, cơ sở có phòng ghi ở đây phải học ở một phòng như vậy, mỗi giờ học không quá sức chứa; tên phòng ghi trong TKB và file TKB phòng. Môn không có phòng nào ghi thì học ở lớp.</t>
+          <t>Không bắt buộc. Mỗi dòng một lớp: cột Lớp ghi tên lớp tùy ý (vd 1/1, 1A, Lá 2), cột Khối ghi tên khối như ở các cột Khối &lt;tên&gt; của sheet CHƯƠNG TRÌNH HỌC (vd 1 hoặc Lá; trống: các chữ số đầu tên lớp), cột Cơ sở ghi tên cơ sở (điểm trường) lớp học, tùy ý, bao nhiêu cơ sở cũng được (trống: Cơ sở 1), cột Nhãn ghi các nhãn tự đặt cách nhau dấu phẩy (vd Song ngữ; không trùng tên lớp): cột Lớp của sheet LUẬT ghi nhãn hay tên cơ sở là mọi lớp có nhãn đó, ở cơ sở đó. Có sheet này thì danh sách lớp lấy ở đây: Chủ Nhiệm ghi Lớp là một lớp của sheet, lớp không có Chủ Nhiệm vẫn được xếp (các môn chia cho GV khác; môn Chỉ GVCN dạy, tiết Luôn do GVCN dạy, tiết HĐTN cố định của GVCN không áp dụng cho lớp đó). Không có sheet này (hoặc sheet trống) thì lớp là lớp của các dòng Chủ Nhiệm, ghi dạng khối/số thứ tự (1/1) hoặc khối rồi tên lớp (1A).</t>
         </is>
       </c>
     </row>
     <row r="46" ht="25" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LUẬT</t>
+          <t>PHÒNG</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Không bắt buộc. Mỗi dòng một phòng học dùng chung (phòng Tin, phòng đa năng, sân trường): cột Phòng ghi tên phòng, cột Cơ sở ghi tên cơ sở như cột Cơ sở của sheet LỚP (trống: Cơ sở 1), cột Môn ghi các môn học ở phòng này cách nhau dấu phẩy (đúng tên trong sheet CHƯƠNG TRÌNH HỌC, hoặc một nhãn môn là tiêu đề một cột Có/Không của sheet đó), cột Khối ghi các khối dùng phòng (trống: mọi khối), cột Sức chứa ghi số lớp học cùng lúc trong phòng (trống: 1; vd sân trường 3). Luật cứng: tiết của môn, khối, cơ sở có phòng ghi ở đây phải học ở một phòng như vậy, mỗi giờ học không quá sức chứa; tên phòng ghi trong TKB và file TKB phòng. Môn không có phòng nào ghi thì học ở lớp.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Không xếp vào</t>
+          <t>LUẬT</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
+          <t>LUẬT: Ở đâu · Không xếp vào</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
+          <t>Môn (của các khối ở cột Khối; để trống: mọi khối) không xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục không xếp vào tiết 1; Tin học không xếp vào Thứ 2. Ghi Giáo viên (chức vụ, Mã GV hoặc họ tên) thì chỉ xét tiết của người đó, để trống Môn là mọi môn: giờ bận, vd Bộ Môn 3 không dạy Thứ 2 tiết 1.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Cố định vào</t>
+          <t>LUẬT: Ở đâu · Chỉ xếp vào</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
+          <t>Môn chỉ xếp vào các ngày, tiết, buổi ghi ở dòng này (ghi ít nhất một trong ba cột), vd Thể dục chỉ xếp vào buổi chiều. Ghi Giáo viên thì chỉ xét tiết của người đó (để trống Môn: mọi môn), vd Bộ Môn 3 chỉ dạy buổi sáng.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="25" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
+          <t>LUẬT: Ở đâu · Cố định vào</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học đúng 1 tiết của Môn ở mỗi giờ ghi ở cột Ngày, Tiết, Buổi, vd Thể dục khối 1 cố định vào Thứ 3 tiết 3.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="25" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa tiết mỗi ngày</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số tiết mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="25" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
+          <t>LUẬT: Bao nhiêu · Giáo viên tối đa lớp mỗi ngày</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
+          <t>Mỗi giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên; để trống: mọi giáo viên) dạy tối đa Số lớp khác nhau mỗi ngày.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="25" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
+          <t>LUẬT: Bao nhiêu · Số lớp học cùng lúc tối đa</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
+          <t>Môn có tối đa Số lớp học cùng một giờ (cả trường, hoặc các khối ở cột Khối), vd phòng Tin học: 1, sân Thể dục: 2.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="25" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
+          <t>LUẬT: Bao nhiêu · Học ít nhất số ngày</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
+          <t>Mỗi lớp học Môn ở ít nhất Số ngày khác nhau trong tuần, vd Tiếng Anh ít nhất 3 ngày.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="25" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học trước</t>
+          <t>LUẬT: Đi cùng nhau · Học 2 tiết liền</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
+          <t>Môn học thành cặp 2 tiết liền, cùng người dạy: mỗi buổi 0 hoặc 2 tiết của môn (tính chung môn tăng cường cùng nhóm), vd Tiếng Anh. Bắt buộc thì số tiết/tuần phải chẵn.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Học cùng giờ</t>
+          <t>LUẬT: Đi cùng nhau · Học trước</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học Môn và các môn ở cột Môn thứ hai cùng giờ, cùng số tiết mỗi tuần, mỗi môn một người dạy, lớp tính một tiết ở giờ đó. Dùng cho lớp chia nhóm, vd nửa lớp học Tin học, nửa lớp học Tiếng Anh; hoặc giáo viên dạy kèm: ghi môn riêng Trợ giảng Tiếng Anh (cùng số tiết, chức vụ Trợ Giảng dạy) học cùng giờ với Tiếng Anh. Chỉ ghi Bắt buộc = Có.</t>
+          <t>Trong một buổi có cả hai môn thì Môn học trước Môn thứ hai, vd Tiếng Việt trước Toán.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Ghép lớp</t>
+          <t>LUẬT: Đi cùng nhau · Học cùng giờ</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Các lớp ghi ở cột Lớp (hoặc các lớp của khối ở cột Khối) học chung Môn: cùng giờ, cùng số tiết mỗi tuần, một người dạy cả nhóm, người đó tính một tiết ở giờ đó, vd Thể dục lớp 3/1, 3/2 học chung một sân. Ghi Môn thứ hai thì lớp có môn đó học chung với các lớp có Môn (mỗi lớp một môn), vd lớp ghép hai khối. Muốn ghép riêng từng khối: dùng Tự ghép, Với mỗi Khối. Chỉ ghi Bắt buộc = Có.</t>
+          <t>Mỗi lớp (của các khối, lớp ghi ở dòng này) học Môn và các môn ở cột Môn thứ hai cùng giờ, cùng số tiết mỗi tuần, mỗi môn một người dạy, lớp tính một tiết ở giờ đó. Dùng cho lớp chia nhóm, vd nửa lớp học Tin học, nửa lớp học Tiếng Anh; hoặc giáo viên dạy kèm: ghi môn riêng Trợ giảng Tiếng Anh (cùng số tiết, chức vụ Trợ Giảng dạy) học cùng giờ với Tiếng Anh. Chỉ ghi Bắt buộc = Có.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
+          <t>LUẬT: Đi cùng nhau · Ghép lớp</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
+          <t>Các lớp ghi ở cột Lớp (hoặc các lớp của khối ở cột Khối) học chung Môn: cùng giờ, cùng số tiết mỗi tuần, một người dạy cả nhóm, người đó tính một tiết ở giờ đó, vd Thể dục lớp 3/1, 3/2 học chung một sân. Ghi Môn thứ hai thì lớp có môn đó học chung với các lớp có Môn (mỗi lớp một môn), vd lớp ghép hai khối. Muốn ghép riêng từng khối: dùng Tự ghép, Với mỗi Khối. Chỉ ghi Bắt buộc = Có.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
+          <t>LUẬT: Ai dạy · Chỉ giáo viên dạy</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Các tiết của Môn (ở các khối, lớp, ngày, tiết ghi ở dòng này) chỉ do giáo viên ghi ở cột Giáo viên dạy: chức vụ, vd Tin học khối 3 chỉ GV Tin Học dạy; hoặc một người (Mã GV hay họ tên) để chọn ai dạy lớp nào, vd Tiếng Anh lớp 3/1 chỉ Tiếng Anh 2 dạy.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
+          <t>LUẬT: Ai dạy · Buổi nghỉ của giáo viên</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
+          <t>Giáo viên không dạy vào các buổi nghỉ ghi ở cột Buổi Nghỉ (sheet NHÂN SỰ) và nghỉ đủ số buổi ghi ở đó. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="25" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép</t>
+          <t>LUẬT: Ai dạy · Giáo viên chỉ dạy cơ sở 2</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
+          <t>Giáo viên không chủ nhiệm ghi Có ở cột Cơ sở 2 hoặc Thai Sản (sheet NHÂN SỰ) chỉ dạy các lớp ở cơ sở 2. Chỉ ghi Bắt buộc = Có; muốn bỏ luật thì xóa dòng hoặc ghi Tạm tắt = Có.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Với mỗi</t>
+          <t>LUẬT: Tự ghép</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
+          <t>Tự ghép câu luật: Với mỗi [phạm vi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Xem các phép đo ở dưới.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="25" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
+          <t>LUẬT: Tự ghép, cột Với mỗi</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
+          <t>Chia các tiết thành từng nhóm theo các chiều, vd 'Lớp, Ngày': luật áp dụng cho mỗi lớp mỗi ngày. Các chiều: Lớp, Giáo viên, Môn, Nhóm môn, Khối, Ngày, Buổi, Giờ học, Cơ sở. Trống: cả trường cả tuần.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
+          <t>LUẬT: Ở đâu · Tự ghép, Phép đo Vị trí</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
+          <t>Các tiết chỉ xếp vào, hoặc không xếp vào, các ngày, tiết, buổi (hoặc giờ có nhãn) ghi ở dòng này. So sánh: Chỉ trong, Không trong.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="25" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số tiết</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
+          <t>Đếm số tiết trong mỗi phạm vi, vd mỗi lớp mỗi ngày học tối đa 1 tiết Toán; mỗi giờ học có tối đa 1 tiết Tin học. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Số khác nhau</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
+          <t>Đếm số lớp, ngày, cơ sở… khác nhau (cột Đếm theo), vd mỗi giáo viên mỗi ngày dạy tối đa 3 lớp; mỗi lớp học Tiếng Anh ít nhất 3 ngày. So sánh: Tối đa, Tối thiểu, Đúng. Ghi cột Số. Ghi cột Đếm theo.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
+          <t>LUẬT: Bao nhiêu · Tự ghép, Phép đo Khoảng cách</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
+          <t>Số tiết trống xen giữa các tiết trong buổi (0: không có tiết trống); hoặc số tiết từ tiết đó đến cuối buổi (0: ở tiết cuối buổi). So sánh: Tiết trống tối đa, Cách cuối buổi tối đa. Ghi cột Số.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Liền nhau</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
+          <t>Các tiết trong một buổi (của mỗi lớp hoặc giáo viên) đứng liền nhau, không có tiết khác xen giữa.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="25" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Theo cặp 2 tiết</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
+          <t>Mỗi buổi học 0 hoặc 2 tiết, 2 tiết đó liền nhau (ưu tiên: hạn chế tiết lẻ đứng một mình).</t>
         </is>
       </c>
     </row>
     <row r="70" ht="25" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Thứ tự</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
+          <t>Trong một buổi (hoặc ngày, nếu Với mỗi có Ngày) tiết của Môn đứng trước (hoặc sau) tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm. So sánh: Trước, Sau.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="25" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Cùng giờ</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Đi kèm</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Các tiết luôn học cùng giờ, cùng số tiết mỗi tuần; chỉ ghi Bắt buộc. Mỗi môn một người (để trống So sánh): mỗi lớp học Môn và Môn thứ hai cùng giờ, lớp tính một tiết ở giờ đó: lớp chia nhóm (mỗi nhóm học một môn, mỗi môn một người dạy) hoặc giáo viên chính và trợ giảng (ghi trợ giảng thành một môn riêng, vd Trợ giảng Tiếng Anh); Với mỗi là Lớp. Cùng một người: ghép lớp, các lớp (của cả trường, hoặc mỗi khối, mỗi cơ sở ở cột Với mỗi) học Môn (và Môn thứ hai nếu ghi) cùng giờ, một người dạy, người đó tính một tiết ở giờ đó. So sánh: Mỗi môn một người, Cùng một người.</t>
+          <t>Buổi (hoặc ngày) có tiết của Môn thì cũng có tiết của Môn thứ hai. Để trống Môn thứ hai và Với mỗi có Nhóm môn: các môn khác cùng nhóm.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="25" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
+          <t>LUẬT: Đi cùng nhau · Tự ghép, Phép đo Cùng giờ</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
+          <t>Các tiết luôn học cùng giờ, cùng số tiết mỗi tuần; chỉ ghi Bắt buộc. Mỗi môn một người (để trống So sánh): mỗi lớp học Môn và Môn thứ hai cùng giờ, lớp tính một tiết ở giờ đó: lớp chia nhóm (mỗi nhóm học một môn, mỗi môn một người dạy) hoặc giáo viên chính và trợ giảng (ghi trợ giảng thành một môn riêng, vd Trợ giảng Tiếng Anh); Với mỗi là Lớp. Cùng một người: ghép lớp, các lớp (của cả trường, hoặc mỗi khối, mỗi cơ sở ở cột Với mỗi) học Môn (và Môn thứ hai nếu ghi) cùng giờ, một người dạy, người đó tính một tiết ở giờ đó. So sánh: Mỗi môn một người, Cùng một người.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="25" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Số</t>
+          <t>LUẬT: Ai dạy · Tự ghép, Phép đo Người dạy</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
+          <t>Các tiết do giáo viên ghi ở cột Giáo viên (chức vụ, Mã GV hoặc họ tên) dạy; hoặc do cùng một người dạy; hoặc hai tiết liền nhau do cùng một người; hoặc tiết đầu tuần do giáo viên đó dạy, tiết của người khác không đứng trước. So sánh: Do, Cùng một người, Liền nhau cùng người, Tiết đầu tuần do.</t>
         </is>
       </c>
     </row>
     <row r="74" ht="25" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
+          <t>LUẬT: Tự ghép, cột Số</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
+          <t>Một số nguyên, hoặc (phép đo Số tiết) một ngưỡng theo dữ liệu: tải ngày, tải ngày + 1, số tiết/tuần chia số ngày (tải ngày: định mức của giáo viên chia theo số tiết của ngày).</t>
         </is>
       </c>
     </row>
     <row r="75" ht="25" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>LUẬT: cấu trúc của TKB</t>
+          <t>LUẬT: Tự ghép, cột Áp dụng khi</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Chỉ áp dụng khi số tiết/tuần của các môn ở cột Môn (phạm vi có Môn, Nhóm môn: của từng môn, nhóm môn) ở khối đó thỏa điều kiện, vd '&gt;= 6, chẵn' (từ 6 tiết trở lên và chẵn) hoặc '&lt;= số ngày' (không quá số ngày học).</t>
         </is>
       </c>
     </row>
     <row r="76" ht="25" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>LUẬT: cấu trúc của TKB</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="25" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
           <t>Kiểu chữ</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Các file kết quả chép kiểu chữ, cỡ chữ, viền của sheet NHÂN SỰ. Chỉ cần chữ và số: không cần công thức, màu nền, ghi chú trong ô hay danh sách thả xuống.</t>
         </is>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -5510,7 +5510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:W35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5534,8 +5534,7 @@
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="9" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="70" customWidth="1" min="23" max="23"/>
+    <col width="70" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -5646,15 +5645,10 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Điểm</t>
+          <t>Tạm tắt</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Tạm tắt</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Luật đọc là</t>
         </is>
@@ -5709,8 +5703,7 @@
       </c>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
-      <c r="W2" s="3" t="n"/>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>Mỗi buổi, một lớp học tối đa 2 tiết của một môn, tính chung môn chính với môn tăng cường cùng nhóm (bắt buộc)</t>
         </is>
@@ -5773,8 +5766,7 @@
       </c>
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
-      <c r="W3" s="3" t="n"/>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>Mỗi ngày, một lớp học tối đa 1 tiết Toán, khi số tiết/tuần của môn không quá số ngày học (bắt buộc)</t>
         </is>
@@ -5831,8 +5823,7 @@
       </c>
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Môn có từ 6 tiết/tuần trở lên và số tiết chẵn, tính chung môn tăng cường cùng nhóm, học thành cặp 2 tiết liền trong buổi; trừ môn có nhãn Không ghép cặp (bắt buộc)</t>
         </is>
@@ -5881,8 +5872,7 @@
       </c>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>Các tiết của một môn trong cùng buổi phải đứng liền nhau (bắt buộc)</t>
         </is>
@@ -5939,8 +5929,7 @@
       </c>
       <c r="U6" s="3" t="n"/>
       <c r="V6" s="3" t="n"/>
-      <c r="W6" s="3" t="n"/>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>Trong một ngày, tiết môn tăng cường đứng sau các tiết môn chính cùng nhóm (bắt buộc)</t>
         </is>
@@ -5993,8 +5982,7 @@
       </c>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>Ngày có tiết môn tăng cường thì cũng có tiết môn chính cùng nhóm (bắt buộc)</t>
         </is>
@@ -6053,8 +6041,7 @@
       </c>
       <c r="U8" s="3" t="n"/>
       <c r="V8" s="3" t="n"/>
-      <c r="W8" s="3" t="n"/>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>Ở mỗi giờ có nhãn Tiết HĐTN cố định, mỗi lớp học đúng 1 tiết HĐTN (bắt buộc)</t>
         </is>
@@ -6107,8 +6094,7 @@
       </c>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>Tiết HĐTN chỉ xếp vào giờ có nhãn Tiết HĐTN cố định hoặc Xếp tiết HĐTN còn lại (bắt buộc)</t>
         </is>
@@ -6169,12 +6155,13 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="n"/>
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>Tiết HĐTN còn lại, ngoài giờ cố định, xếp ở tiết cuối buổi (ưu tiên thấp)</t>
         </is>
@@ -6231,8 +6218,7 @@
       </c>
       <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
-      <c r="X11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>Ở giờ có nhãn Luôn do GVCN dạy, lớp học với GV chủ nhiệm (bắt buộc)</t>
         </is>
@@ -6289,8 +6275,7 @@
       </c>
       <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="n"/>
-      <c r="W12" s="3" t="n"/>
-      <c r="X12" s="2" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>Môn có nhãn Chỉ GVCN dạy thì chỉ GV chủ nhiệm dạy (bắt buộc)</t>
         </is>
@@ -6343,8 +6328,7 @@
       </c>
       <c r="U13" s="3" t="n"/>
       <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n"/>
-      <c r="X13" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>Hai tiết liền nhau của một môn (cùng nhóm) trong buổi do cùng một giáo viên dạy (bắt buộc)</t>
         </is>
@@ -6405,8 +6389,7 @@
       </c>
       <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="2" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>Môn có nhãn GVCN nhận trọn: tiết đầu tuần của lớp do GV chủ nhiệm dạy, tiết của giáo viên khác không đứng trước (bắt buộc)</t>
         </is>
@@ -6447,8 +6430,7 @@
       </c>
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>Giáo viên không dạy vào buổi nghỉ ghi ở cột Buổi Nghỉ và nghỉ đủ số buổi ghi ở đó (bắt buộc)</t>
         </is>
@@ -6507,8 +6489,7 @@
       </c>
       <c r="U16" s="3" t="n"/>
       <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>Mỗi buổi, một giáo viên chỉ dạy ở một cơ sở (bắt buộc)</t>
         </is>
@@ -6565,12 +6546,13 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="U17" s="3" t="n"/>
-      <c r="V17" s="3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="W17" s="3" t="n"/>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>Rất cao</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="n"/>
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>Hạn chế để một giáo viên đổi cơ sở trong cùng một ngày (dạy ở hai cơ sở trở lên) (ưu tiên rất cao)</t>
         </is>
@@ -6611,8 +6593,7 @@
       </c>
       <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="n"/>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>Giáo viên không chủ nhiệm ghi Cơ sở 2 hoặc Thai Sản chỉ dạy các lớp ở cơ sở 2 (bắt buộc)</t>
         </is>
@@ -6663,12 +6644,13 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="U19" s="3" t="n"/>
-      <c r="V19" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="W19" s="3" t="n"/>
-      <c r="X19" s="2" t="inlineStr">
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="n"/>
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>Tránh xếp môn có nhãn Môn nặng vào giờ có nhãn Hạn chế môn nặng (ưu tiên cao)</t>
         </is>
@@ -6723,12 +6705,13 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="U20" s="3" t="n"/>
-      <c r="V20" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="W20" s="3" t="n"/>
-      <c r="X20" s="2" t="inlineStr">
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="n"/>
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>Môn có nhãn Ưu tiên buổi sáng xếp vào buổi sáng (ưu tiên vừa)</t>
         </is>
@@ -6783,12 +6766,13 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="W21" s="3" t="n"/>
-      <c r="X21" s="2" t="inlineStr">
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="n"/>
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>Số tiết mỗi ngày của giáo viên không quá tải ngày, tức số tiết/tuần chia đều cho các ngày (ưu tiên thấp)</t>
         </is>
@@ -6843,12 +6827,13 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="U22" s="3" t="n"/>
-      <c r="V22" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="W22" s="3" t="n"/>
-      <c r="X22" s="2" t="inlineStr">
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>Vừa</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="n"/>
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>Số tiết mỗi ngày của giáo viên không quá tải ngày + 1 tiết (ưu tiên vừa)</t>
         </is>
@@ -6907,12 +6892,13 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="U23" s="3" t="n"/>
-      <c r="V23" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="2" t="inlineStr">
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="n"/>
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>Mỗi môn, trừ HĐTN và môn ưu tiên buổi sáng, rải đều trong tuần: một ngày không quá số tiết/tuần chia số ngày (ưu tiên thấp)</t>
         </is>
@@ -6975,12 +6961,13 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="U24" s="3" t="n"/>
-      <c r="V24" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="W24" s="3" t="n"/>
-      <c r="X24" s="2" t="inlineStr">
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="n"/>
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>Môn ưu tiên buổi sáng rải đều trong tuần: một ngày không quá số tiết/tuần chia số ngày (ưu tiên thấp)</t>
         </is>
@@ -7037,12 +7024,13 @@
           <t>Không</t>
         </is>
       </c>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="2" t="inlineStr">
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>Thấp</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="n"/>
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>Giáo viên, trừ GV chủ nhiệm, không có tiết trống xen giữa các tiết trong buổi (ưu tiên thấp)</t>
         </is>
@@ -7071,8 +7059,7 @@
       <c r="T26" s="3" t="n"/>
       <c r="U26" s="3" t="n"/>
       <c r="V26" s="3" t="n"/>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="2" t="n"/>
+      <c r="W26" s="2" t="n"/>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="n"/>
@@ -7097,8 +7084,7 @@
       <c r="T27" s="3" t="n"/>
       <c r="U27" s="3" t="n"/>
       <c r="V27" s="3" t="n"/>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="2" t="n"/>
+      <c r="W27" s="2" t="n"/>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="n"/>
@@ -7123,8 +7109,7 @@
       <c r="T28" s="3" t="n"/>
       <c r="U28" s="3" t="n"/>
       <c r="V28" s="3" t="n"/>
-      <c r="W28" s="3" t="n"/>
-      <c r="X28" s="2" t="n"/>
+      <c r="W28" s="2" t="n"/>
     </row>
     <row r="29" ht="25" customHeight="1">
       <c r="A29" s="2" t="n"/>
@@ -7149,8 +7134,7 @@
       <c r="T29" s="3" t="n"/>
       <c r="U29" s="3" t="n"/>
       <c r="V29" s="3" t="n"/>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" s="2" t="n"/>
+      <c r="W29" s="2" t="n"/>
     </row>
     <row r="30" ht="25" customHeight="1">
       <c r="A30" s="2" t="n"/>
@@ -7175,8 +7159,7 @@
       <c r="T30" s="3" t="n"/>
       <c r="U30" s="3" t="n"/>
       <c r="V30" s="3" t="n"/>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="2" t="n"/>
+      <c r="W30" s="2" t="n"/>
     </row>
     <row r="31" ht="25" customHeight="1">
       <c r="A31" s="2" t="n"/>
@@ -7201,8 +7184,7 @@
       <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n"/>
       <c r="V31" s="3" t="n"/>
-      <c r="W31" s="3" t="n"/>
-      <c r="X31" s="2" t="n"/>
+      <c r="W31" s="2" t="n"/>
     </row>
     <row r="32" ht="25" customHeight="1">
       <c r="A32" s="2" t="n"/>
@@ -7227,8 +7209,7 @@
       <c r="T32" s="3" t="n"/>
       <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="2" t="n"/>
+      <c r="W32" s="2" t="n"/>
     </row>
     <row r="33" ht="25" customHeight="1">
       <c r="A33" s="2" t="n"/>
@@ -7253,8 +7234,7 @@
       <c r="T33" s="3" t="n"/>
       <c r="U33" s="3" t="n"/>
       <c r="V33" s="3" t="n"/>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="2" t="n"/>
+      <c r="W33" s="2" t="n"/>
     </row>
     <row r="34" ht="25" customHeight="1">
       <c r="A34" s="2" t="n"/>
@@ -7279,8 +7259,7 @@
       <c r="T34" s="3" t="n"/>
       <c r="U34" s="3" t="n"/>
       <c r="V34" s="3" t="n"/>
-      <c r="W34" s="3" t="n"/>
-      <c r="X34" s="2" t="n"/>
+      <c r="W34" s="2" t="n"/>
     </row>
     <row r="35" ht="25" customHeight="1">
       <c r="A35" s="2" t="n"/>
@@ -7305,8 +7284,7 @@
       <c r="T35" s="3" t="n"/>
       <c r="U35" s="3" t="n"/>
       <c r="V35" s="3" t="n"/>
-      <c r="W35" s="3" t="n"/>
-      <c r="X35" s="2" t="n"/>
+      <c r="W35" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7886,7 +7864,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Điểm để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên ghi Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm) hoặc ghi thẳng Điểm (điểm trừ mỗi lần không theo). Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
+          <t>Mọi luật xếp TKB, mỗi dòng một luật, đọc như một câu: Với mỗi [cột Với mỗi] · các tiết [Môn, Nhãn, Khối, Lớp, Ngày, Tiết, Buổi, Giáo viên] · thì [Phép đo] [So sánh] [Số] · khi [Áp dụng khi]. Mỗi luật trả lời một trong bốn câu hỏi: Ở đâu, Bao nhiêu, Đi cùng nhau, Ai dạy (các kiểu luật và phép đo xếp theo câu hỏi ở dưới). File mẫu ghi sẵn các luật có sẵn của chương trình: sửa số hoặc Mức để chỉnh, đổi Bắt buộc, xóa dòng để bỏ luật (hoặc ghi Có ở cột Tạm tắt: chương trình bỏ qua dòng đó mà vẫn giữ lại, xóa chữ Có là dùng lại), thêm dòng để có luật mới. Cột Nhóm và Luật đọc là chỉ để đọc (chương trình ghi lại mỗi lần). Kiểu luật: một mẫu hoặc Tự ghép; cột kiểu luật không dùng để trống. Bắt buộc: Có (luật cứng) hoặc Không (ưu tiên); luật ưu tiên chọn Mức Thấp, Vừa, Cao, Rất cao (100, 400, 1500, 5000 điểm trừ mỗi lần không theo; luật có sẵn để nguyên mức mặc định thì dùng điểm đã chỉnh sẵn của luật đó). File cũ có cột Điểm (điểm trừ ghi thẳng) vẫn đọc được. Môn, Lớp, Khối, Ngày, Tiết ghi danh sách cách nhau bằng dấu phẩy hoặc khoảng, vd 3, 4 hoặc 3-5; Thứ 2, Thứ 4 hoặc T2-T4; 5-7. Buổi: Sáng hoặc Chiều. Giáo viên: chức vụ (Chủ Nhiệm, Bộ Môn, Quản Lý hoặc chức vụ GV chuyên biệt), 'trừ Chủ Nhiệm' là mọi giáo viên trừ chức vụ đó; hoặc một người: Mã GV (vd Bộ Môn 3, Chủ Nhiệm 1/1, đánh số theo thứ tự dòng của sheet NHÂN SỰ) hay họ tên (hai người trùng tên thì ghi Mã GV), vd giờ bận: Không xếp vào, Giáo viên Bộ Môn 3, Thứ 2, tiết 1 (để trống Môn); ép phân công: Chỉ giáo viên dạy, Môn Tiếng Anh, Lớp 3/1, Giáo viên Tiếng Anh 2. Câu đọc lại ghi Mã GV, không ghi họ tên. Nhãn, Trừ nhãn: tên các cột Có/Không của môn (vd Môn nặng) hoặc của giờ học (ngày, tiết, vd Luôn do GVCN dạy); nhiều nhãn giờ học là giờ có một trong các nhãn. Gồm môn tăng cường: Có thì Môn tính cả các môn tăng cường cùng nhóm. Không có sheet này thì chương trình dùng các luật có sẵn và sheet LUẬT RIÊNG (file của bản trước).</t>
         </is>
       </c>
     </row>

--- a/data/Input_Template_V8.xlsx
+++ b/data/Input_Template_V8.xlsx
@@ -1855,7 +1855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1983,1194 +1983,224 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n"/>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
       <c r="N2" s="3" t="n"/>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
+      <c r="Q2" s="3" t="n"/>
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" s="3" t="n"/>
+      <c r="T2" s="3" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Toán</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n"/>
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Hoạt động trải nghiệm</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>HĐTN</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>3</v>
-      </c>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>4</v>
-      </c>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
       <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
     </row>
     <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt tăng cường</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="n"/>
       <c r="B8" s="3" t="n"/>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>TV tăng cường</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
       <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
+      <c r="Q8" s="3" t="n"/>
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" s="3" t="n"/>
+      <c r="T8" s="3" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="n"/>
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Tự nhiên xã hội</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="n"/>
       <c r="B10" s="3" t="n"/>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>TNXH</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
       <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="O10" s="3" t="n"/>
       <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="Q10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="n"/>
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Tin học</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
-      <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n"/>
-      <c r="R18" s="3" t="n"/>
-      <c r="S18" s="3" t="n"/>
-      <c r="T18" s="3" t="n"/>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
-      <c r="R19" s="3" t="n"/>
-      <c r="S19" s="3" t="n"/>
-      <c r="T19" s="3" t="n"/>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
-      <c r="P20" s="3" t="n"/>
-      <c r="Q20" s="3" t="n"/>
-      <c r="R20" s="3" t="n"/>
-      <c r="S20" s="3" t="n"/>
-      <c r="T20" s="3" t="n"/>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n"/>
-      <c r="T21" s="3" t="n"/>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="3" t="n"/>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="n"/>
-      <c r="R22" s="3" t="n"/>
-      <c r="S22" s="3" t="n"/>
-      <c r="T22" s="3" t="n"/>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="3" t="n"/>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" s="3" t="n"/>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" s="3" t="n"/>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="n"/>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="3" t="n"/>
-      <c r="S24" s="3" t="n"/>
-      <c r="T24" s="3" t="n"/>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="n"/>
-    </row>
-    <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
-      <c r="Q26" s="3" t="n"/>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5292,9 +4322,7 @@
       <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Không</t>
@@ -5316,7 +4344,7 @@
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -5335,7 +4363,7 @@
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -5354,7 +4382,7 @@
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -5367,10 +4395,10 @@
       <c r="B10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n">
-        <v>4</v>
-      </c>
+      <c r="C10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Không</t>
@@ -5400,7 +4428,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -5495,7 +4523,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Có</t>
+          <t>Không</t>
         </is>
       </c>
     </row>
@@ -5510,7 +4538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5655,21 +4683,9 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Bảo vệ học sinh</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Nhóm môn, Buổi</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
@@ -5680,56 +4696,22 @@
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>Số tiết</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>Tối đa</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="N2" s="3" t="n"/>
+      <c r="O2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n"/>
       <c r="R2" s="3" t="n"/>
       <c r="S2" s="3" t="n"/>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="T2" s="3" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi buổi, một lớp học tối đa 2 tiết của một môn, tính chung môn chính với môn tăng cường cùng nhóm (bắt buộc)</t>
-        </is>
-      </c>
+      <c r="W2" s="2" t="n"/>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Bảo vệ học sinh</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Ngày</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Toán</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
@@ -5739,112 +4721,46 @@
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Số tiết</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Tối đa</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
       <c r="Q3" s="3" t="n"/>
       <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>&lt;= số ngày</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi ngày, một lớp học tối đa 1 tiết Toán, khi số tiết/tuần của môn không quá số ngày học (bắt buộc)</t>
-        </is>
-      </c>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Bảo vệ học sinh</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Nhóm môn, Buổi</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Không ghép cặp</t>
-        </is>
-      </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Theo cặp 2 tiết</t>
-        </is>
-      </c>
+      <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>&gt;= 6, chẵn</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="n"/>
       <c r="V4" s="3" t="n"/>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>Môn có từ 6 tiết/tuần trở lên và số tiết chẵn, tính chung môn tăng cường cùng nhóm, học thành cặp 2 tiết liền trong buổi; trừ môn có nhãn Không ghép cặp (bắt buộc)</t>
-        </is>
-      </c>
+      <c r="W4" s="2" t="n"/>
     </row>
     <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Bảo vệ học sinh</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Môn</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
@@ -5855,52 +4771,24 @@
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>Liền nhau</t>
-        </is>
-      </c>
+      <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="n"/>
       <c r="R5" s="3" t="n"/>
       <c r="S5" s="3" t="n"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>Các tiết của một môn trong cùng buổi phải đứng liền nhau (bắt buộc)</t>
-        </is>
-      </c>
+      <c r="W5" s="2" t="n"/>
     </row>
     <row r="6" ht="25" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Bảo vệ học sinh</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Nhóm môn, Ngày</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Môn tăng cường</t>
-        </is>
-      </c>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
@@ -5908,56 +4796,24 @@
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>Thứ tự</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>Sau</t>
-        </is>
-      </c>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
       <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="n"/>
       <c r="R6" s="3" t="n"/>
       <c r="S6" s="3" t="n"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="n"/>
       <c r="V6" s="3" t="n"/>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>Trong một ngày, tiết môn tăng cường đứng sau các tiết môn chính cùng nhóm (bắt buộc)</t>
-        </is>
-      </c>
+      <c r="W6" s="2" t="n"/>
     </row>
     <row r="7" ht="25" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Bảo vệ học sinh</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Nhóm môn, Ngày</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Môn tăng cường</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
@@ -5965,52 +4821,24 @@
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>Đi kèm</t>
-        </is>
-      </c>
+      <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="n"/>
       <c r="Q7" s="3" t="n"/>
       <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="n"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>Ngày có tiết môn tăng cường thì cũng có tiết môn chính cùng nhóm (bắt buộc)</t>
-        </is>
-      </c>
+      <c r="W7" s="2" t="n"/>
     </row>
     <row r="8" ht="25" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN và GVCN</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Giờ học</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Môn HĐTN, Tiết HĐTN cố định</t>
-        </is>
-      </c>
+      <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
@@ -6018,54 +4846,24 @@
       <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>Số tiết</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>Đúng</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
       <c r="Q8" s="3" t="n"/>
       <c r="R8" s="3" t="n"/>
       <c r="S8" s="3" t="n"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="T8" s="3" t="n"/>
       <c r="U8" s="3" t="n"/>
       <c r="V8" s="3" t="n"/>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>Ở mỗi giờ có nhãn Tiết HĐTN cố định, mỗi lớp học đúng 1 tiết HĐTN (bắt buộc)</t>
-        </is>
-      </c>
+      <c r="W8" s="2" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN và GVCN</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Môn HĐTN, Xếp tiết HĐTN còn lại, Tiết HĐTN cố định</t>
-        </is>
-      </c>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
@@ -6073,1218 +4871,66 @@
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Vị trí</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ trong</t>
-        </is>
-      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n"/>
       <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n"/>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Tiết HĐTN chỉ xếp vào giờ có nhãn Tiết HĐTN cố định hoặc Xếp tiết HĐTN còn lại (bắt buộc)</t>
-        </is>
-      </c>
+      <c r="W9" s="2" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN và GVCN</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Lớp</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Môn HĐTN, Xếp tiết HĐTN còn lại</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Tiết HĐTN cố định</t>
-        </is>
-      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>Khoảng cách</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>Cách cuối buổi tối đa</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n"/>
       <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n"/>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>Tiết HĐTN còn lại, ngoài giờ cố định, xếp ở tiết cuối buổi (ưu tiên thấp)</t>
-        </is>
-      </c>
+      <c r="W10" s="2" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN và GVCN</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Luôn do GVCN dạy</t>
-        </is>
-      </c>
+      <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Chủ Nhiệm</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>Người dạy</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>Do</t>
-        </is>
-      </c>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="n"/>
       <c r="Q11" s="3" t="n"/>
       <c r="R11" s="3" t="n"/>
       <c r="S11" s="3" t="n"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
+      <c r="T11" s="3" t="n"/>
       <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Ở giờ có nhãn Luôn do GVCN dạy, lớp học với GV chủ nhiệm (bắt buộc)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN và GVCN</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ GVCN dạy</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Chủ Nhiệm</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>Người dạy</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>Do</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3" t="n"/>
-      <c r="R12" s="3" t="n"/>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="n"/>
-      <c r="V12" s="3" t="n"/>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>Môn có nhãn Chỉ GVCN dạy thì chỉ GV chủ nhiệm dạy (bắt buộc)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Người dạy</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Nhóm môn, Buổi</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>Người dạy</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>Liền nhau cùng người</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" s="3" t="n"/>
-      <c r="S13" s="3" t="n"/>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="n"/>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>Hai tiết liền nhau của một môn (cùng nhóm) trong buổi do cùng một giáo viên dạy (bắt buộc)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Người dạy</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Nhóm môn</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>GVCN nhận trọn</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>Chủ Nhiệm</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>Người dạy</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>Tiết đầu tuần do</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>Môn có nhãn GVCN nhận trọn: tiết đầu tuần của lớp do GV chủ nhiệm dạy, tiết của giáo viên khác không đứng trước (bắt buộc)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Lịch giáo viên</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Buổi nghỉ của giáo viên</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="n"/>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>Giáo viên không dạy vào buổi nghỉ ghi ở cột Buổi Nghỉ và nghỉ đủ số buổi ghi ở đó (bắt buộc)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Lịch giáo viên</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Giáo viên, Buổi</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>Số khác nhau</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>Tối đa</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>Cơ sở</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="n"/>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi buổi, một giáo viên chỉ dạy ở một cơ sở (bắt buộc)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Lịch giáo viên</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Giáo viên, Ngày</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>Số khác nhau</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>Tối đa</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t>Cơ sở</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>Rất cao</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="n"/>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>Hạn chế để một giáo viên đổi cơ sở trong cùng một ngày (dạy ở hai cơ sở trở lên) (ưu tiên rất cao)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Lịch giáo viên</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Giáo viên chỉ dạy cơ sở 2</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n"/>
-      <c r="R18" s="3" t="n"/>
-      <c r="S18" s="3" t="n"/>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="n"/>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>Giáo viên không chủ nhiệm ghi Cơ sở 2 hoặc Thai Sản chỉ dạy các lớp ở cơ sở 2 (bắt buộc)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="25" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên khi xếp giờ</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Môn nặng, Hạn chế môn nặng</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>Vị trí</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>Không trong</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
-      <c r="R19" s="3" t="n"/>
-      <c r="S19" s="3" t="n"/>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t>Cao</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="n"/>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>Tránh xếp môn có nhãn Môn nặng vào giờ có nhãn Hạn chế môn nặng (ưu tiên cao)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="25" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên khi xếp giờ</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Ưu tiên buổi sáng</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>Sáng</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>Vị trí</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>Chỉ trong</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n"/>
-      <c r="Q20" s="3" t="n"/>
-      <c r="R20" s="3" t="n"/>
-      <c r="S20" s="3" t="n"/>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="n"/>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>Môn có nhãn Ưu tiên buổi sáng xếp vào buổi sáng (ưu tiên vừa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên khi xếp giờ</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Giáo viên, Ngày</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>Số tiết</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>Tối đa</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>tải ngày</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n"/>
-      <c r="T21" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="n"/>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>Số tiết mỗi ngày của giáo viên không quá tải ngày, tức số tiết/tuần chia đều cho các ngày (ưu tiên thấp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên khi xếp giờ</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Giáo viên, Ngày</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>Số tiết</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>Tối đa</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t>tải ngày + 1</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="n"/>
-      <c r="R22" s="3" t="n"/>
-      <c r="S22" s="3" t="n"/>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t>Vừa</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="n"/>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>Số tiết mỗi ngày của giáo viên không quá tải ngày + 1 tiết (ưu tiên vừa)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên khi xếp giờ</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Môn, Ngày</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Môn HĐTN, Ưu tiên buổi sáng</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>Số tiết</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>Tối đa</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>số tiết/tuần chia số ngày</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" s="3" t="n"/>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>Mỗi môn, trừ HĐTN và môn ưu tiên buổi sáng, rải đều trong tuần: một ngày không quá số tiết/tuần chia số ngày (ưu tiên thấp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên khi xếp giờ</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Lớp, Môn, Ngày</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Ưu tiên buổi sáng</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Môn HĐTN</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>Số tiết</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>Tối đa</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>số tiết/tuần chia số ngày</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="3" t="n"/>
-      <c r="S24" s="3" t="n"/>
-      <c r="T24" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="V24" s="3" t="n"/>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>Môn ưu tiên buổi sáng rải đều trong tuần: một ngày không quá số tiết/tuần chia số ngày (ưu tiên thấp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Ưu tiên khi xếp giờ</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Tự ghép</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Giáo viên, Buổi</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>trừ Chủ Nhiệm</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>Khoảng cách</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>Tiết trống tối đa</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t>Không</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t>Thấp</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>Giáo viên, trừ GV chủ nhiệm, không có tiết trống xen giữa các tiết trong buổi (ưu tiên thấp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
-      <c r="Q26" s="3" t="n"/>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
-      <c r="U26" s="3" t="n"/>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="25" customHeight="1">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="n"/>
-      <c r="Q27" s="3" t="n"/>
-      <c r="R27" s="3" t="n"/>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" s="3" t="n"/>
-      <c r="U27" s="3" t="n"/>
-      <c r="V27" s="3" t="n"/>
-      <c r="W27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="25" customHeight="1">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
-      <c r="P28" s="3" t="n"/>
-      <c r="Q28" s="3" t="n"/>
-      <c r="R28" s="3" t="n"/>
-      <c r="S28" s="3" t="n"/>
-      <c r="T28" s="3" t="n"/>
-      <c r="U28" s="3" t="n"/>
-      <c r="V28" s="3" t="n"/>
-      <c r="W28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="25" customHeight="1">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="n"/>
-      <c r="Q29" s="3" t="n"/>
-      <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n"/>
-      <c r="T29" s="3" t="n"/>
-      <c r="U29" s="3" t="n"/>
-      <c r="V29" s="3" t="n"/>
-      <c r="W29" s="2" t="n"/>
-    </row>
-    <row r="30" ht="25" customHeight="1">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="3" t="n"/>
-      <c r="Q30" s="3" t="n"/>
-      <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n"/>
-      <c r="U30" s="3" t="n"/>
-      <c r="V30" s="3" t="n"/>
-      <c r="W30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="25" customHeight="1">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
-      <c r="P31" s="3" t="n"/>
-      <c r="Q31" s="3" t="n"/>
-      <c r="R31" s="3" t="n"/>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="3" t="n"/>
-      <c r="U31" s="3" t="n"/>
-      <c r="V31" s="3" t="n"/>
-      <c r="W31" s="2" t="n"/>
-    </row>
-    <row r="32" ht="25" customHeight="1">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="3" t="n"/>
-      <c r="Q32" s="3" t="n"/>
-      <c r="R32" s="3" t="n"/>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="3" t="n"/>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="2" t="n"/>
-    </row>
-    <row r="33" ht="25" customHeight="1">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n"/>
-      <c r="Q33" s="3" t="n"/>
-      <c r="R33" s="3" t="n"/>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n"/>
-      <c r="U33" s="3" t="n"/>
-      <c r="V33" s="3" t="n"/>
-      <c r="W33" s="2" t="n"/>
-    </row>
-    <row r="34" ht="25" customHeight="1">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
-      <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="3" t="n"/>
-      <c r="R34" s="3" t="n"/>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" s="3" t="n"/>
-      <c r="U34" s="3" t="n"/>
-      <c r="V34" s="3" t="n"/>
-      <c r="W34" s="2" t="n"/>
-    </row>
-    <row r="35" ht="25" customHeight="1">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="n"/>
-      <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" s="3" t="n"/>
-      <c r="S35" s="3" t="n"/>
-      <c r="T35" s="3" t="n"/>
-      <c r="U35" s="3" t="n"/>
-      <c r="V35" s="3" t="n"/>
-      <c r="W35" s="2" t="n"/>
+      <c r="W11" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8212,7 +5858,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ).</t>
+          <t>Cấu trúc của TKB (không phải luật, luôn có): mỗi lớp mỗi giờ học một tiết; mỗi lớp học đủ số tiết của chương trình học; giáo viên không dạy hai nơi cùng lúc, dạy không quá định mức (cộng số tiết bù tối đa ở chế độ bù giờ), Quản Lý dạy đúng định mức; giáo viên chỉ dạy các môn chức vụ được dạy (sheet CHƯƠNG TRÌNH HỌC, CHỨC VỤ); giáo viên không dạy buổi nghỉ ghi ở cột Buổi Nghỉ và nghỉ đủ số buổi ghi ở đó; giáo viên không chủ nhiệm ghi Cơ sở 2 hoặc Thai Sản chỉ dạy các lớp ở cơ sở 2 (sheet NHÂN SỰ).</t>
         </is>
       </c>
     </row>
